--- a/assets/3D/setup.xlsx
+++ b/assets/3D/setup.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\assets\3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048CD627-3D18-4419-9C58-1E37C295613E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA972E6-B9AB-41A2-91E4-5FC98C80BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17247,7 +17247,7 @@
         <v>300</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>70</v>
@@ -17316,8 +17316,8 @@
       <c r="G4">
         <v>150</v>
       </c>
-      <c r="H4">
-        <v>3</v>
+      <c r="H4" s="4">
+        <v>5</v>
       </c>
       <c r="I4">
         <v>70</v>
@@ -17351,7 +17351,7 @@
       <c r="G5">
         <v>100</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="4">
         <v>5</v>
       </c>
       <c r="I5">
@@ -17386,8 +17386,8 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>3</v>
+      <c r="H6" s="4">
+        <v>5</v>
       </c>
       <c r="I6">
         <v>70</v>

--- a/assets/3D/setup.xlsx
+++ b/assets/3D/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\ConfinedLab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\assets\3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA972E6-B9AB-41A2-91E4-5FC98C80BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2ED8D6-9F64-4364-8E29-86BA27B7F423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11422" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="352">
   <si>
     <t>nlay</t>
   </si>
@@ -1088,6 +1088,18 @@
   </si>
   <si>
     <t>10k yrs time steps for 1M years</t>
+  </si>
+  <si>
+    <t>Manual refinement</t>
+  </si>
+  <si>
+    <t>Adaptive time step</t>
+  </si>
+  <si>
+    <t>t1 (days)</t>
+  </si>
+  <si>
+    <t>perlen (years)</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1211,6 +1223,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1527,9 +1545,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1583,9 +1601,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -1602,7 +1620,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -1620,7 +1638,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>56</v>
       </c>
@@ -1638,7 +1656,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1656,7 +1674,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -1674,7 +1692,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
@@ -1691,7 +1709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>66</v>
       </c>
@@ -1717,12 +1735,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AM364"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.46484375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>123</v>
       </c>
@@ -1814,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -1910,7 +1928,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -2102,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -2198,7 +2216,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -2279,7 +2297,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -2345,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>134</v>
       </c>
@@ -2411,7 +2429,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>135</v>
       </c>
@@ -2477,7 +2495,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>136</v>
       </c>
@@ -2543,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>137</v>
       </c>
@@ -2613,7 +2631,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -2682,7 +2700,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -2751,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -2820,7 +2838,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -2886,7 +2904,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>142</v>
       </c>
@@ -2952,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -3018,7 +3036,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>145</v>
       </c>
@@ -3087,7 +3105,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>147</v>
       </c>
@@ -3141,7 +3159,7 @@
         <v>5.5502136001665456E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -3213,7 +3231,7 @@
         <v>7.1790398823913721E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>149</v>
       </c>
@@ -3285,7 +3303,7 @@
         <v>6.247710440845614E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -3357,7 +3375,7 @@
         <v>7.1853251477000421E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -3429,7 +3447,7 @@
         <v>6.9554227893998163E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -3483,7 +3501,7 @@
         <v>5.7253061645059339E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>153</v>
       </c>
@@ -3552,7 +3570,7 @@
         <v>7.5562383814068183E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>154</v>
       </c>
@@ -3621,7 +3639,7 @@
         <v>4.7956646402789609E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -3690,7 +3708,7 @@
         <v>3.77861344903145E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>157</v>
       </c>
@@ -3759,7 +3777,7 @@
         <v>6.3076157488416986E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -3828,7 +3846,7 @@
         <v>5.3573866388844803E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>161</v>
       </c>
@@ -3897,7 +3915,7 @@
         <v>5.1650487503666432E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>163</v>
       </c>
@@ -3966,7 +3984,7 @@
         <v>6.206520086059846E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>165</v>
       </c>
@@ -4020,7 +4038,7 @@
         <v>7.195322821158302E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>166</v>
       </c>
@@ -4074,7 +4092,7 @@
         <v>2.9134882445236649E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -4128,7 +4146,7 @@
         <v>5.0209969717145185E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>168</v>
       </c>
@@ -4182,7 +4200,7 @@
         <v>7.4802277554614563E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>169</v>
       </c>
@@ -4236,7 +4254,7 @@
         <v>5.6061012672548299E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>170</v>
       </c>
@@ -4290,7 +4308,7 @@
         <v>8.2964178446747177E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>171</v>
       </c>
@@ -4344,7 +4362,7 @@
         <v>5.5192525783438826E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>172</v>
       </c>
@@ -4398,7 +4416,7 @@
         <v>2.594301690595899E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>173</v>
       </c>
@@ -4452,7 +4470,7 @@
         <v>5.8758806918154829E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>174</v>
       </c>
@@ -4506,7 +4524,7 @@
         <v>7.1827862361545337E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>175</v>
       </c>
@@ -4560,7 +4578,7 @@
         <v>6.3964240766474305E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>176</v>
       </c>
@@ -4614,7 +4632,7 @@
         <v>6.4218380286974329E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>177</v>
       </c>
@@ -4668,7 +4686,7 @@
         <v>7.9556383137322937E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>178</v>
       </c>
@@ -4722,7 +4740,7 @@
         <v>4.7143997174482332E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>179</v>
       </c>
@@ -4806,7 +4824,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>180</v>
       </c>
@@ -4890,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>181</v>
       </c>
@@ -4974,7 +4992,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>182</v>
       </c>
@@ -5058,7 +5076,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>183</v>
       </c>
@@ -5142,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>184</v>
       </c>
@@ -5226,7 +5244,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>185</v>
       </c>
@@ -5310,7 +5328,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>186</v>
       </c>
@@ -5394,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>187</v>
       </c>
@@ -5478,7 +5496,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>188</v>
       </c>
@@ -5562,7 +5580,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>189</v>
       </c>
@@ -5646,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>190</v>
       </c>
@@ -5730,7 +5748,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>191</v>
       </c>
@@ -5814,7 +5832,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>192</v>
       </c>
@@ -5898,7 +5916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>193</v>
       </c>
@@ -5982,7 +6000,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>194</v>
       </c>
@@ -6066,7 +6084,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>195</v>
       </c>
@@ -6120,7 +6138,7 @@
         <v>4.2985466508481168E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>196</v>
       </c>
@@ -6174,7 +6192,7 @@
         <v>3.0854060773305718E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -6228,7 +6246,7 @@
         <v>5.7701883542728865E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>198</v>
       </c>
@@ -6281,8 +6299,11 @@
         <f t="shared" si="7"/>
         <v>8.4426260266278266E-4</v>
       </c>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD65" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>199</v>
       </c>
@@ -6335,8 +6356,23 @@
         <f t="shared" ref="AA66:AA97" si="11">+W66</f>
         <v>9.552168804465085E-4</v>
       </c>
-    </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE66" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF66" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH66" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>200</v>
       </c>
@@ -6389,8 +6425,23 @@
         <f t="shared" si="11"/>
         <v>3.5786093692759128E-4</v>
       </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG67" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH67" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>201</v>
       </c>
@@ -6443,8 +6494,23 @@
         <f t="shared" si="11"/>
         <v>9.5065057852621645E-4</v>
       </c>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD68" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="4">
+        <v>3600000</v>
+      </c>
+      <c r="AF68" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG68" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>202</v>
       </c>
@@ -6497,8 +6563,23 @@
         <f t="shared" si="11"/>
         <v>4.7094307374518279E-4</v>
       </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD69" s="4">
+        <v>2</v>
+      </c>
+      <c r="AE69" s="4">
+        <v>18000</v>
+      </c>
+      <c r="AF69" s="4">
+        <v>600</v>
+      </c>
+      <c r="AG69" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH69" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>203</v>
       </c>
@@ -6551,8 +6632,23 @@
         <f t="shared" si="11"/>
         <v>7.0474477053287924E-4</v>
       </c>
-    </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD70" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE70" s="4">
+        <v>180000</v>
+      </c>
+      <c r="AF70" s="4">
+        <v>500</v>
+      </c>
+      <c r="AG70" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH70" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>204</v>
       </c>
@@ -6605,8 +6701,23 @@
         <f t="shared" si="11"/>
         <v>6.47540851284781E-4</v>
       </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD71" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE71" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="AF71" s="4">
+        <v>100</v>
+      </c>
+      <c r="AG71" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH71" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="72" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>205</v>
       </c>
@@ -6659,8 +6770,23 @@
         <f t="shared" si="11"/>
         <v>9.4119160098010126E-4</v>
       </c>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD72" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="4">
+        <v>360000000</v>
+      </c>
+      <c r="AF72" s="4">
+        <v>100</v>
+      </c>
+      <c r="AG72" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH72" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>206</v>
       </c>
@@ -6714,7 +6840,7 @@
         <v>5.0662494239123103E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>207</v>
       </c>
@@ -6767,8 +6893,16 @@
         <f t="shared" si="11"/>
         <v>5.5343966107292586E-4</v>
       </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD74" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="AE74" s="4"/>
+      <c r="AF74" s="4"/>
+      <c r="AG74" s="4"/>
+      <c r="AH74" s="4"/>
+      <c r="AI74" s="4"/>
+    </row>
+    <row r="75" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>208</v>
       </c>
@@ -6821,8 +6955,26 @@
         <f t="shared" si="11"/>
         <v>6.3697425558412722E-4</v>
       </c>
-    </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE75" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF75" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH75" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI75" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>209</v>
       </c>
@@ -6875,8 +7027,27 @@
         <f t="shared" si="11"/>
         <v>7.291229427225874E-4</v>
       </c>
-    </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD76" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="4">
+        <v>180000</v>
+      </c>
+      <c r="AF76" s="4">
+        <v>200</v>
+      </c>
+      <c r="AG76" s="4">
+        <v>1.0255057211429901</v>
+      </c>
+      <c r="AH76" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI76" s="4">
+        <f>AE76/360</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>210</v>
       </c>
@@ -6929,8 +7100,27 @@
         <f t="shared" si="11"/>
         <v>6.4225139746381982E-4</v>
       </c>
-    </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD77" s="4">
+        <v>2</v>
+      </c>
+      <c r="AE77" s="4">
+        <v>1800000</v>
+      </c>
+      <c r="AF77" s="4">
+        <v>200</v>
+      </c>
+      <c r="AG77" s="4">
+        <v>1.0396382277644101</v>
+      </c>
+      <c r="AH77" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI77" s="4">
+        <f>AE77/360</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>211</v>
       </c>
@@ -6983,8 +7173,27 @@
         <f t="shared" si="11"/>
         <v>4.8630228955171201E-4</v>
       </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD78" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE78" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="AF78" s="4">
+        <v>200</v>
+      </c>
+      <c r="AG78" s="4">
+        <v>1.0532256549825301</v>
+      </c>
+      <c r="AH78" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI78" s="4">
+        <f>AE78/360</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>212</v>
       </c>
@@ -7037,8 +7246,27 @@
         <f t="shared" si="11"/>
         <v>7.8134219163826664E-4</v>
       </c>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD79" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE79" s="4">
+        <v>180000000</v>
+      </c>
+      <c r="AF79" s="4">
+        <v>200</v>
+      </c>
+      <c r="AG79" s="4">
+        <v>1.0666174958886401</v>
+      </c>
+      <c r="AH79" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI79" s="4">
+        <f>AE79/360</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>213</v>
       </c>
@@ -7091,8 +7319,27 @@
         <f t="shared" si="11"/>
         <v>5.8506117777726231E-4</v>
       </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD80" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE80" s="4">
+        <v>720000000</v>
+      </c>
+      <c r="AF80" s="4">
+        <v>200</v>
+      </c>
+      <c r="AG80" s="4">
+        <v>1.0746477694404</v>
+      </c>
+      <c r="AH80" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI80" s="4">
+        <f>AE80/360</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -7145,8 +7392,14 @@
         <f t="shared" si="11"/>
         <v>6.370758623671785E-4</v>
       </c>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD81" s="4"/>
+      <c r="AE81" s="4"/>
+      <c r="AF81" s="4"/>
+      <c r="AG81" s="4"/>
+      <c r="AH81" s="4"/>
+      <c r="AI81" s="4"/>
+    </row>
+    <row r="82" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>215</v>
       </c>
@@ -7199,8 +7452,26 @@
         <f t="shared" si="11"/>
         <v>8.0515352214514436E-4</v>
       </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD82" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE82" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF82" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH82" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI82" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="83" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>216</v>
       </c>
@@ -7253,8 +7524,27 @@
         <f t="shared" si="11"/>
         <v>5.750724982417129E-4</v>
       </c>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD83" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE83" s="4">
+        <v>180000</v>
+      </c>
+      <c r="AF83" s="8">
+        <v>200</v>
+      </c>
+      <c r="AG83" s="8">
+        <v>1.0373939999999999</v>
+      </c>
+      <c r="AH83" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI83" s="4">
+        <f>AE83/360</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>217</v>
       </c>
@@ -7307,8 +7597,27 @@
         <f t="shared" si="11"/>
         <v>6.7040596663695798E-4</v>
       </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD84" s="8">
+        <v>2</v>
+      </c>
+      <c r="AE84" s="4">
+        <v>1800000</v>
+      </c>
+      <c r="AF84" s="8">
+        <v>200</v>
+      </c>
+      <c r="AG84" s="8">
+        <v>1.052738</v>
+      </c>
+      <c r="AH84" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI84" s="4">
+        <f>AE84/360</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>218</v>
       </c>
@@ -7361,8 +7670,27 @@
         <f t="shared" si="11"/>
         <v>6.6752831004103605E-4</v>
       </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD85" s="8">
+        <v>3</v>
+      </c>
+      <c r="AE85" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="AF85" s="8">
+        <v>200</v>
+      </c>
+      <c r="AG85" s="8">
+        <v>1.0680700000000001</v>
+      </c>
+      <c r="AH85" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI85" s="4">
+        <f>AE85/360</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>219</v>
       </c>
@@ -7415,8 +7743,27 @@
         <f t="shared" si="11"/>
         <v>6.8681608077582183E-4</v>
       </c>
-    </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD86" s="8">
+        <v>4</v>
+      </c>
+      <c r="AE86" s="4">
+        <v>180000000</v>
+      </c>
+      <c r="AF86" s="8">
+        <v>200</v>
+      </c>
+      <c r="AG86" s="8">
+        <v>1.0834010000000001</v>
+      </c>
+      <c r="AH86" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI86" s="4">
+        <f>AE86/360</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>220</v>
       </c>
@@ -7469,8 +7816,27 @@
         <f t="shared" si="11"/>
         <v>8.5098987706838051E-4</v>
       </c>
-    </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD87" s="8">
+        <v>5</v>
+      </c>
+      <c r="AE87" s="4">
+        <v>720000000</v>
+      </c>
+      <c r="AF87" s="8">
+        <v>200</v>
+      </c>
+      <c r="AG87" s="8">
+        <v>1.0909169999999999</v>
+      </c>
+      <c r="AH87" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI87" s="4">
+        <f>AE87/360</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>221</v>
       </c>
@@ -7524,7 +7890,7 @@
         <v>6.7755654381398901E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>222</v>
       </c>
@@ -7578,7 +7944,7 @@
         <v>9.4339543613295384E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>223</v>
       </c>
@@ -7632,7 +7998,7 @@
         <v>5.8085408169564559E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>224</v>
       </c>
@@ -7686,7 +8052,7 @@
         <v>3.6120501290660029E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>225</v>
       </c>
@@ -7740,7 +8106,7 @@
         <v>6.2975536923403231E-4</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>226</v>
       </c>
@@ -7794,7 +8160,7 @@
         <v>7.228323272845125E-4</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>227</v>
       </c>
@@ -7848,7 +8214,7 @@
         <v>4.6803677487896461E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>228</v>
       </c>
@@ -7902,7 +8268,7 @@
         <v>7.7336905885629418E-4</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>229</v>
       </c>
@@ -7956,7 +8322,7 @@
         <v>5.6237098746364077E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>230</v>
       </c>
@@ -8010,7 +8376,7 @@
         <v>8.1362777910270177E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>231</v>
       </c>
@@ -8064,7 +8430,7 @@
         <v>4.356087488178263E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>232</v>
       </c>
@@ -8118,7 +8484,7 @@
         <v>1.0028195602172999E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>233</v>
       </c>
@@ -8172,7 +8538,7 @@
         <v>5.0364788225881177E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>234</v>
       </c>
@@ -8226,7 +8592,7 @@
         <v>7.9643019829107138E-4</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>235</v>
       </c>
@@ -8280,7 +8646,7 @@
         <v>4.7180228576033662E-4</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>236</v>
       </c>
@@ -8334,7 +8700,7 @@
         <v>6.1373542849109256E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>237</v>
       </c>
@@ -8388,7 +8754,7 @@
         <v>6.4311012308476624E-4</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>238</v>
       </c>
@@ -8442,7 +8808,7 @@
         <v>6.2770310871303756E-4</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>239</v>
       </c>
@@ -8496,7 +8862,7 @@
         <v>5.7559569640524308E-4</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>240</v>
       </c>
@@ -8550,7 +8916,7 @@
         <v>5.3332641124062639E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>241</v>
       </c>
@@ -8604,7 +8970,7 @@
         <v>8.2728508003655082E-4</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>242</v>
       </c>
@@ -8658,7 +9024,7 @@
         <v>9.7268368705790624E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>243</v>
       </c>
@@ -8712,7 +9078,7 @@
         <v>4.8961483057842047E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>244</v>
       </c>
@@ -8766,7 +9132,7 @@
         <v>5.6725746685323385E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>245</v>
       </c>
@@ -8820,7 +9186,7 @@
         <v>5.7586134556664864E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>246</v>
       </c>
@@ -8874,7 +9240,7 @@
         <v>6.64750588599489E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>247</v>
       </c>
@@ -8928,7 +9294,7 @@
         <v>9.4712108096549959E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>248</v>
       </c>
@@ -8982,7 +9348,7 @@
         <v>5.5438130895789643E-4</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>249</v>
       </c>
@@ -9036,7 +9402,7 @@
         <v>9.0184342071178349E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>250</v>
       </c>
@@ -9090,7 +9456,7 @@
         <v>6.2612911789142764E-4</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>251</v>
       </c>
@@ -9144,7 +9510,7 @@
         <v>7.5873173424928584E-4</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>252</v>
       </c>
@@ -9198,7 +9564,7 @@
         <v>6.1259290710490542E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>253</v>
       </c>
@@ -9252,7 +9618,7 @@
         <v>6.9084118394068103E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>254</v>
       </c>
@@ -9306,7 +9672,7 @@
         <v>6.6669851278469488E-4</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>255</v>
       </c>
@@ -9360,7 +9726,7 @@
         <v>8.2045218583240757E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>256</v>
       </c>
@@ -9414,7 +9780,7 @@
         <v>5.2081387235738941E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>257</v>
       </c>
@@ -9468,7 +9834,7 @@
         <v>5.7189465431413248E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>258</v>
       </c>
@@ -9522,7 +9888,7 @@
         <v>9.1233097501937279E-4</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>259</v>
       </c>
@@ -9576,7 +9942,7 @@
         <v>5.1138621680753824E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>260</v>
       </c>
@@ -9630,7 +9996,7 @@
         <v>5.834401472729541E-4</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>261</v>
       </c>
@@ -9684,7 +10050,7 @@
         <v>7.1160228947361758E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>262</v>
       </c>
@@ -9738,7 +10104,7 @@
         <v>6.7192904177343729E-4</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>263</v>
       </c>
@@ -9792,7 +10158,7 @@
         <v>6.8402164621609858E-4</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>264</v>
       </c>
@@ -9846,7 +10212,7 @@
         <v>7.3510433221211555E-4</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>265</v>
       </c>
@@ -9900,7 +10266,7 @@
         <v>6.8958168854050443E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>266</v>
       </c>
@@ -9954,7 +10320,7 @@
         <v>7.0175093423377206E-4</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -10008,7 +10374,7 @@
         <v>9.24392529713391E-4</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>268</v>
       </c>
@@ -10062,7 +10428,7 @@
         <v>4.2679489394130968E-4</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>269</v>
       </c>
@@ -10116,7 +10482,7 @@
         <v>7.0492044974188462E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>270</v>
       </c>
@@ -10170,7 +10536,7 @@
         <v>6.0317831663807579E-4</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>271</v>
       </c>
@@ -10224,7 +10590,7 @@
         <v>5.3431529879549361E-4</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>272</v>
       </c>
@@ -10278,7 +10644,7 @@
         <v>9.2650687165257131E-4</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>273</v>
       </c>
@@ -10332,7 +10698,7 @@
         <v>4.9093461376614072E-4</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>274</v>
       </c>
@@ -10386,7 +10752,7 @@
         <v>4.6471042769603648E-4</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -10440,7 +10806,7 @@
         <v>3.9116170433328728E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>276</v>
       </c>
@@ -10494,7 +10860,7 @@
         <v>4.0431038289007962E-4</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>277</v>
       </c>
@@ -10548,7 +10914,7 @@
         <v>6.785411243790979E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>278</v>
       </c>
@@ -10602,7 +10968,7 @@
         <v>7.2348983877483703E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>279</v>
       </c>
@@ -10656,7 +11022,7 @@
         <v>6.5532909863160892E-4</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>280</v>
       </c>
@@ -10710,7 +11076,7 @@
         <v>7.5474341979737567E-4</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>281</v>
       </c>
@@ -10764,7 +11130,7 @@
         <v>5.7669688744116539E-4</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>282</v>
       </c>
@@ -10818,7 +11184,7 @@
         <v>8.0697176066542612E-4</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>283</v>
       </c>
@@ -10872,7 +11238,7 @@
         <v>6.0999509381094925E-4</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>284</v>
       </c>
@@ -10926,7 +11292,7 @@
         <v>5.3117803129513444E-4</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>285</v>
       </c>
@@ -10980,7 +11346,7 @@
         <v>6.8402085428227407E-4</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>286</v>
       </c>
@@ -11034,7 +11400,7 @@
         <v>5.6115552392589597E-4</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>287</v>
       </c>
@@ -11088,7 +11454,7 @@
         <v>5.6175108458420442E-4</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>288</v>
       </c>
@@ -11117,7 +11483,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>289</v>
       </c>
@@ -11146,7 +11512,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>290</v>
       </c>
@@ -11175,7 +11541,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>291</v>
       </c>
@@ -11204,7 +11570,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>292</v>
       </c>
@@ -11233,7 +11599,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>293</v>
       </c>
@@ -11262,7 +11628,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>294</v>
       </c>
@@ -11291,7 +11657,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>295</v>
       </c>
@@ -11320,7 +11686,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>296</v>
       </c>
@@ -11349,7 +11715,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>297</v>
       </c>
@@ -11378,7 +11744,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>298</v>
       </c>
@@ -11407,7 +11773,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>299</v>
       </c>
@@ -11436,7 +11802,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>300</v>
       </c>
@@ -11465,7 +11831,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>301</v>
       </c>
@@ -11494,7 +11860,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>302</v>
       </c>
@@ -11523,7 +11889,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>303</v>
       </c>
@@ -11552,7 +11918,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>304</v>
       </c>
@@ -11581,7 +11947,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>305</v>
       </c>
@@ -11610,7 +11976,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>306</v>
       </c>
@@ -11639,7 +12005,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>307</v>
       </c>
@@ -11668,7 +12034,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>308</v>
       </c>
@@ -11697,7 +12063,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>309</v>
       </c>
@@ -11726,7 +12092,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>310</v>
       </c>
@@ -11755,7 +12121,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>311</v>
       </c>
@@ -11784,7 +12150,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>312</v>
       </c>
@@ -11813,7 +12179,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>313</v>
       </c>
@@ -11842,7 +12208,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>314</v>
       </c>
@@ -11871,7 +12237,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>315</v>
       </c>
@@ -11900,7 +12266,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>316</v>
       </c>
@@ -11929,7 +12295,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>317</v>
       </c>
@@ -11958,7 +12324,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>318</v>
       </c>
@@ -11987,7 +12353,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>319</v>
       </c>
@@ -12016,7 +12382,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>320</v>
       </c>
@@ -12045,7 +12411,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>321</v>
       </c>
@@ -12074,7 +12440,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>322</v>
       </c>
@@ -12103,7 +12469,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>323</v>
       </c>
@@ -12132,7 +12498,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>324</v>
       </c>
@@ -12161,7 +12527,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>325</v>
       </c>
@@ -12190,7 +12556,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>326</v>
       </c>
@@ -12219,7 +12585,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>327</v>
       </c>
@@ -12248,7 +12614,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>328</v>
       </c>
@@ -12277,7 +12643,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>329</v>
       </c>
@@ -12306,7 +12672,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>330</v>
       </c>
@@ -12335,7 +12701,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>331</v>
       </c>
@@ -12364,7 +12730,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>332</v>
       </c>
@@ -12393,7 +12759,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>333</v>
       </c>
@@ -12422,7 +12788,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>334</v>
       </c>
@@ -12451,7 +12817,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>335</v>
       </c>
@@ -12480,7 +12846,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>336</v>
       </c>
@@ -12509,7 +12875,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>337</v>
       </c>
@@ -12538,7 +12904,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>338</v>
       </c>
@@ -12567,7 +12933,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>339</v>
       </c>
@@ -12596,7 +12962,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>340</v>
       </c>
@@ -12625,7 +12991,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>341</v>
       </c>
@@ -12654,7 +13020,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>342</v>
       </c>
@@ -12683,7 +13049,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>343</v>
       </c>
@@ -12712,7 +13078,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>344</v>
       </c>
@@ -12741,7 +13107,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>1950</v>
       </c>
@@ -12770,7 +13136,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>1951</v>
       </c>
@@ -12799,7 +13165,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>1952</v>
       </c>
@@ -12828,7 +13194,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>1953</v>
       </c>
@@ -12857,7 +13223,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>1954</v>
       </c>
@@ -12886,7 +13252,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>1955</v>
       </c>
@@ -12915,7 +13281,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>1956</v>
       </c>
@@ -12944,7 +13310,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>1957</v>
       </c>
@@ -12973,7 +13339,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>1958</v>
       </c>
@@ -13002,7 +13368,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>1959</v>
       </c>
@@ -13031,7 +13397,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>1960</v>
       </c>
@@ -13060,7 +13426,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>1961</v>
       </c>
@@ -13089,7 +13455,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>1962</v>
       </c>
@@ -13118,7 +13484,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>1963</v>
       </c>
@@ -13147,7 +13513,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>1964</v>
       </c>
@@ -13176,7 +13542,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>1965</v>
       </c>
@@ -13205,7 +13571,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>1966</v>
       </c>
@@ -13234,7 +13600,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>1967</v>
       </c>
@@ -13263,7 +13629,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>1968</v>
       </c>
@@ -13292,7 +13658,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>1969</v>
       </c>
@@ -13321,7 +13687,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>1970</v>
       </c>
@@ -13350,7 +13716,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>1971</v>
       </c>
@@ -13379,7 +13745,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>1972</v>
       </c>
@@ -13408,7 +13774,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>1973</v>
       </c>
@@ -13437,7 +13803,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>1974</v>
       </c>
@@ -13466,7 +13832,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>1975</v>
       </c>
@@ -13495,7 +13861,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>1976</v>
       </c>
@@ -13524,7 +13890,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>1977</v>
       </c>
@@ -13553,7 +13919,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>1978</v>
       </c>
@@ -13582,7 +13948,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>1979</v>
       </c>
@@ -13611,7 +13977,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>1980</v>
       </c>
@@ -13640,7 +14006,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>1981</v>
       </c>
@@ -13669,7 +14035,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>1982</v>
       </c>
@@ -13698,7 +14064,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>1983</v>
       </c>
@@ -13727,7 +14093,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>1984</v>
       </c>
@@ -13756,7 +14122,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>1985</v>
       </c>
@@ -13785,7 +14151,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>1986</v>
       </c>
@@ -13814,7 +14180,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>1987</v>
       </c>
@@ -13843,7 +14209,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>1988</v>
       </c>
@@ -13872,7 +14238,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>1989</v>
       </c>
@@ -13901,7 +14267,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>1990</v>
       </c>
@@ -13930,7 +14296,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>1991</v>
       </c>
@@ -13959,7 +14325,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>1992</v>
       </c>
@@ -13988,7 +14354,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>1993</v>
       </c>
@@ -14017,7 +14383,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>1994</v>
       </c>
@@ -14046,7 +14412,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>1995</v>
       </c>
@@ -14075,7 +14441,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>1996</v>
       </c>
@@ -14104,7 +14470,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>1997</v>
       </c>
@@ -14133,7 +14499,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>1998</v>
       </c>
@@ -14162,7 +14528,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>1999</v>
       </c>
@@ -14191,7 +14557,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>2000</v>
       </c>
@@ -14220,7 +14586,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>2001</v>
       </c>
@@ -14249,7 +14615,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>2002</v>
       </c>
@@ -14278,7 +14644,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>2003</v>
       </c>
@@ -14307,7 +14673,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>2004</v>
       </c>
@@ -14336,7 +14702,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>2005</v>
       </c>
@@ -14365,7 +14731,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>2006</v>
       </c>
@@ -14394,7 +14760,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>2007</v>
       </c>
@@ -14423,7 +14789,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>2008</v>
       </c>
@@ -14452,7 +14818,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>2009</v>
       </c>
@@ -14481,7 +14847,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>2010</v>
       </c>
@@ -14510,7 +14876,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>2011</v>
       </c>
@@ -14539,7 +14905,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>2012</v>
       </c>
@@ -14568,7 +14934,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>2013</v>
       </c>
@@ -14597,7 +14963,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>2014</v>
       </c>
@@ -14626,7 +14992,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>2015</v>
       </c>
@@ -14655,7 +15021,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>2016</v>
       </c>
@@ -14684,7 +15050,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>2017</v>
       </c>
@@ -14713,7 +15079,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>2018</v>
       </c>
@@ -14742,7 +15108,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>2019</v>
       </c>
@@ -14771,7 +15137,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>2020</v>
       </c>
@@ -14800,7 +15166,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>2021</v>
       </c>
@@ -14829,7 +15195,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>2022</v>
       </c>
@@ -14858,7 +15224,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>2023</v>
       </c>
@@ -14887,7 +15253,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>2024</v>
       </c>
@@ -14916,7 +15282,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>2025</v>
       </c>
@@ -14945,7 +15311,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>2026</v>
       </c>
@@ -14974,7 +15340,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>2027</v>
       </c>
@@ -15003,7 +15369,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>2028</v>
       </c>
@@ -15032,7 +15398,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>2029</v>
       </c>
@@ -15061,7 +15427,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>2030</v>
       </c>
@@ -15090,7 +15456,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>2031</v>
       </c>
@@ -15119,7 +15485,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>2032</v>
       </c>
@@ -15148,7 +15514,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>2033</v>
       </c>
@@ -15177,7 +15543,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>2034</v>
       </c>
@@ -15206,7 +15572,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>2035</v>
       </c>
@@ -15235,7 +15601,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>2036</v>
       </c>
@@ -15264,7 +15630,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>2037</v>
       </c>
@@ -15293,7 +15659,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>2038</v>
       </c>
@@ -15322,7 +15688,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>2039</v>
       </c>
@@ -15351,7 +15717,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>2040</v>
       </c>
@@ -15380,7 +15746,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>2041</v>
       </c>
@@ -15409,7 +15775,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>2042</v>
       </c>
@@ -15438,7 +15804,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>2043</v>
       </c>
@@ -15467,7 +15833,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>2044</v>
       </c>
@@ -15496,7 +15862,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>2045</v>
       </c>
@@ -15525,7 +15891,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>2046</v>
       </c>
@@ -15554,7 +15920,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>2047</v>
       </c>
@@ -15583,7 +15949,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>2048</v>
       </c>
@@ -15612,7 +15978,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>2049</v>
       </c>
@@ -15641,7 +16007,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>2050</v>
       </c>
@@ -15670,7 +16036,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>2051</v>
       </c>
@@ -15699,7 +16065,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>2052</v>
       </c>
@@ -15728,7 +16094,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>2053</v>
       </c>
@@ -15757,7 +16123,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>2054</v>
       </c>
@@ -15786,7 +16152,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>2055</v>
       </c>
@@ -15815,7 +16181,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>2056</v>
       </c>
@@ -15844,7 +16210,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>2057</v>
       </c>
@@ -15873,7 +16239,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>2058</v>
       </c>
@@ -15902,7 +16268,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>2059</v>
       </c>
@@ -15931,7 +16297,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>2060</v>
       </c>
@@ -15960,7 +16326,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>2061</v>
       </c>
@@ -15989,7 +16355,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>2062</v>
       </c>
@@ -16018,7 +16384,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>2063</v>
       </c>
@@ -16047,7 +16413,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>2064</v>
       </c>
@@ -16076,7 +16442,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>2065</v>
       </c>
@@ -16105,7 +16471,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>2066</v>
       </c>
@@ -16134,7 +16500,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>2067</v>
       </c>
@@ -16163,7 +16529,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>2068</v>
       </c>
@@ -16192,7 +16558,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>2069</v>
       </c>
@@ -16221,7 +16587,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>2070</v>
       </c>
@@ -16250,7 +16616,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>2071</v>
       </c>
@@ -16279,7 +16645,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>2072</v>
       </c>
@@ -16308,7 +16674,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>2073</v>
       </c>
@@ -16337,7 +16703,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>2074</v>
       </c>
@@ -16366,7 +16732,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>2075</v>
       </c>
@@ -16395,7 +16761,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>2076</v>
       </c>
@@ -16424,7 +16790,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>2077</v>
       </c>
@@ -16453,7 +16819,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>2078</v>
       </c>
@@ -16482,7 +16848,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>2079</v>
       </c>
@@ -16511,7 +16877,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>2080</v>
       </c>
@@ -16540,7 +16906,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>2081</v>
       </c>
@@ -16569,7 +16935,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>2082</v>
       </c>
@@ -16598,7 +16964,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>2083</v>
       </c>
@@ -16627,7 +16993,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>2084</v>
       </c>
@@ -16656,7 +17022,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>2085</v>
       </c>
@@ -16685,7 +17051,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>2086</v>
       </c>
@@ -16714,7 +17080,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>2087</v>
       </c>
@@ -16743,7 +17109,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>2088</v>
       </c>
@@ -16772,7 +17138,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>2089</v>
       </c>
@@ -16801,7 +17167,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>2090</v>
       </c>
@@ -16830,7 +17196,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>2091</v>
       </c>
@@ -16859,7 +17225,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>2092</v>
       </c>
@@ -16888,7 +17254,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>2093</v>
       </c>
@@ -16917,7 +17283,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>2094</v>
       </c>
@@ -16946,7 +17312,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>2095</v>
       </c>
@@ -16975,7 +17341,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>2096</v>
       </c>
@@ -17004,7 +17370,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>2097</v>
       </c>
@@ -17033,7 +17399,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>2098</v>
       </c>
@@ -17062,7 +17428,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>2099</v>
       </c>
@@ -17091,7 +17457,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>2100</v>
       </c>
@@ -17120,7 +17486,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>345</v>
       </c>
@@ -17149,7 +17515,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B364">
         <v>20000000</v>
       </c>
@@ -17178,18 +17544,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="5.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.453125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="5.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.53125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.06640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.46484375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -17224,7 +17590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -17259,7 +17625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -17294,7 +17660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -17329,7 +17695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -17364,7 +17730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -17407,12 +17773,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E364"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="40.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.9296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -17429,7 +17795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -17446,7 +17812,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1</v>
       </c>
@@ -17463,1143 +17829,1099 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>18000</v>
-      </c>
-      <c r="C4">
-        <v>600</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>180000</v>
-      </c>
-      <c r="C5">
-        <v>500</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>18000000</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>360000000</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="4">
+        <v>720000000</v>
+      </c>
+      <c r="C4" s="4">
+        <v>200</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.0909169999999999</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" s="2"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" s="2"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" s="2"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" s="2"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" s="2"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" s="2"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" s="2"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" s="2"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" s="2"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" s="2"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" s="2"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" s="2"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" s="2"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A59" s="2"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A60" s="2"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A61" s="2"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A62" s="2"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A64" s="2"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" s="2"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A66" s="2"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A67" s="2"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A68" s="2"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A69" s="2"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A70" s="2"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A71" s="2"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A72" s="2"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A73" s="2"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A74" s="2"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A75" s="2"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A76" s="2"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A77" s="2"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A78" s="2"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A79" s="2"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A80" s="2"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A81" s="2"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A82" s="2"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A83" s="2"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A84" s="2"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A85" s="2"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A86" s="2"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A87" s="2"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A88" s="2"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A89" s="2"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A90" s="2"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A91" s="2"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A92" s="2"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A93" s="2"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A94" s="2"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A95" s="2"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A96" s="2"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A97" s="2"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A98" s="2"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A99" s="2"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A101" s="2"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A102" s="2"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A103" s="2"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A104" s="2"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A105" s="2"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A106" s="2"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A107" s="2"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A108" s="2"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A109" s="2"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A110" s="2"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A111" s="2"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A112" s="2"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A113" s="2"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A114" s="2"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A115" s="2"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A116" s="2"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A117" s="2"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A118" s="2"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A119" s="2"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A120" s="2"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A121" s="2"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A122" s="2"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A123" s="2"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A124" s="2"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A125" s="2"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A126" s="2"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A127" s="2"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A128" s="2"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A129" s="2"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A130" s="2"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A131" s="2"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A132" s="2"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A133" s="2"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A134" s="2"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A135" s="2"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A136" s="2"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A137" s="2"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A138" s="2"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A139" s="2"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A140" s="2"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A141" s="2"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A142" s="2"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A143" s="2"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A144" s="2"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A145" s="2"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A146" s="2"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A147" s="2"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A148" s="2"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A149" s="2"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A150" s="2"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A151" s="2"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A152" s="2"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A153" s="2"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A154" s="2"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A155" s="2"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A156" s="2"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A157" s="2"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A158" s="2"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A159" s="2"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A160" s="2"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A161" s="2"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A162" s="2"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A163" s="2"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A164" s="2"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A165" s="2"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A166" s="2"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A167" s="2"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A168" s="2"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A169" s="2"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A170" s="2"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A171" s="2"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A172" s="2"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A173" s="2"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A174" s="2"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A175" s="2"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A176" s="2"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A177" s="2"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A178" s="2"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A179" s="2"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A180" s="2"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A181" s="2"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A182" s="2"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A183" s="2"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A184" s="2"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A185" s="2"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A186" s="2"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A187" s="2"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A188" s="2"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A189" s="2"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A190" s="2"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A191" s="2"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A192" s="2"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A193" s="2"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A194" s="2"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A195" s="2"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A196" s="2"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A197" s="2"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A198" s="2"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A199" s="2"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A200" s="2"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A201" s="2"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A202" s="2"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A203" s="2"/>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A204" s="2"/>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A205" s="2"/>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A206" s="2"/>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A207" s="2"/>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A208" s="2"/>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A209" s="2"/>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A210" s="2"/>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A211" s="2"/>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A212" s="2"/>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A213" s="2"/>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A214" s="2"/>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A215" s="2"/>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A216" s="2"/>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A217" s="2"/>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A218" s="2"/>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A219" s="2"/>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A220" s="2"/>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A221" s="2"/>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A222" s="2"/>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A223" s="2"/>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A224" s="2"/>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A225" s="2"/>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A226" s="2"/>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A227" s="2"/>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A228" s="2"/>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A229" s="2"/>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A230" s="2"/>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A231" s="2"/>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A232" s="2"/>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A233" s="2"/>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A234" s="2"/>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A235" s="2"/>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A236" s="2"/>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A237" s="2"/>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A238" s="2"/>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A239" s="2"/>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A240" s="2"/>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A241" s="2"/>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A242" s="2"/>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A243" s="2"/>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A244" s="2"/>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A245" s="2"/>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A246" s="2"/>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A247" s="2"/>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A248" s="2"/>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A249" s="2"/>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A250" s="2"/>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A251" s="2"/>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A252" s="2"/>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A253" s="2"/>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A254" s="2"/>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A255" s="2"/>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A256" s="2"/>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A257" s="2"/>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A258" s="2"/>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A259" s="2"/>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A260" s="2"/>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A261" s="2"/>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A262" s="2"/>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A263" s="2"/>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A264" s="2"/>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A265" s="2"/>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A266" s="2"/>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A267" s="2"/>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A268" s="2"/>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A269" s="2"/>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A270" s="2"/>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A271" s="2"/>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A272" s="2"/>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A273" s="2"/>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A274" s="2"/>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A275" s="2"/>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A276" s="2"/>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A277" s="2"/>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A278" s="2"/>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A279" s="2"/>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A280" s="2"/>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A281" s="2"/>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A282" s="2"/>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A283" s="2"/>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A284" s="2"/>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A285" s="2"/>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A286" s="2"/>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A287" s="2"/>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A288" s="2"/>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A289" s="2"/>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A290" s="2"/>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A291" s="2"/>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A292" s="2"/>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A293" s="2"/>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A294" s="2"/>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A295" s="2"/>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A296" s="2"/>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A297" s="2"/>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A298" s="2"/>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A299" s="2"/>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A300" s="2"/>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A301" s="2"/>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A302" s="2"/>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A303" s="2"/>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A304" s="2"/>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A305" s="2"/>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A306" s="2"/>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A307" s="2"/>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A308" s="2"/>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A309" s="2"/>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A310" s="2"/>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A311" s="2"/>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A312" s="2"/>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A313" s="2"/>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A314" s="2"/>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A315" s="2"/>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A316" s="2"/>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A317" s="2"/>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A318" s="2"/>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A319" s="2"/>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A320" s="2"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A321" s="2"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A322" s="2"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A323" s="2"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A324" s="2"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A325" s="2"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A326" s="2"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A327" s="2"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A328" s="2"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A329" s="2"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A330" s="2"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A331" s="2"/>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A332" s="2"/>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A333" s="2"/>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A334" s="2"/>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A335" s="2"/>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A336" s="2"/>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A337" s="2"/>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A338" s="2"/>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A339" s="2"/>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A340" s="2"/>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A341" s="2"/>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A342" s="2"/>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A343" s="2"/>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A344" s="2"/>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A345" s="2"/>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A346" s="2"/>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A347" s="2"/>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A348" s="2"/>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A349" s="2"/>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A350" s="2"/>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A351" s="2"/>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A352" s="2"/>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A353" s="2"/>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A354" s="2"/>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A355" s="2"/>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A356" s="2"/>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A357" s="2"/>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A358" s="2"/>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A359" s="2"/>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A360" s="2"/>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A361" s="2"/>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A362" s="2"/>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A363" s="2"/>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A364" s="2"/>
     </row>
   </sheetData>
@@ -18610,9 +18932,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L363"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>37</v>
       </c>
@@ -18632,7 +18954,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -18657,7 +18979,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>3600000</v>
       </c>
@@ -18682,7 +19004,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>400000000</v>
       </c>
@@ -18703,7 +19025,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -18711,21 +19033,21 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -18733,7 +19055,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -18741,7 +19063,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -18749,7 +19071,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -18757,7 +19079,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -18765,7 +19087,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -18773,7 +19095,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -18781,7 +19103,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -18789,7 +19111,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -18797,7 +19119,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -18805,7 +19127,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -18813,7 +19135,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -18821,7 +19143,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -18829,7 +19151,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -18837,7 +19159,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -18845,7 +19167,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -18853,7 +19175,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -18861,7 +19183,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -18869,7 +19191,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -18877,7 +19199,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -18885,7 +19207,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -18893,7 +19215,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -18901,7 +19223,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -18909,7 +19231,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -18917,7 +19239,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -18925,7 +19247,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -18933,7 +19255,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -18941,7 +19263,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -18949,7 +19271,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -18957,7 +19279,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -18965,7 +19287,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -18973,7 +19295,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -18981,7 +19303,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -18989,7 +19311,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -18997,7 +19319,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -19005,7 +19327,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -19013,7 +19335,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -19021,7 +19343,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -19029,7 +19351,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -19037,7 +19359,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -19045,7 +19367,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -19053,7 +19375,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -19061,7 +19383,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -19069,7 +19391,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -19077,7 +19399,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -19085,7 +19407,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -19093,7 +19415,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -19101,7 +19423,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -19109,7 +19431,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -19117,7 +19439,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -19125,7 +19447,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -19133,7 +19455,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -19141,7 +19463,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -19149,7 +19471,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -19157,7 +19479,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -19165,7 +19487,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -19173,7 +19495,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -19181,7 +19503,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -19189,7 +19511,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -19197,7 +19519,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -19205,7 +19527,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -19213,7 +19535,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -19221,7 +19543,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -19229,7 +19551,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -19237,7 +19559,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -19245,7 +19567,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -19253,7 +19575,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -19261,7 +19583,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -19269,7 +19591,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -19277,7 +19599,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -19285,7 +19607,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -19293,7 +19615,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -19301,7 +19623,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -19309,7 +19631,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -19317,7 +19639,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -19325,7 +19647,7 @@
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -19333,7 +19655,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -19341,7 +19663,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -19349,7 +19671,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -19357,7 +19679,7 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -19365,7 +19687,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -19373,7 +19695,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -19381,7 +19703,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -19389,7 +19711,7 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -19397,7 +19719,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -19405,7 +19727,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -19413,7 +19735,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -19421,7 +19743,7 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -19429,7 +19751,7 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -19437,7 +19759,7 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -19445,7 +19767,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -19453,7 +19775,7 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -19461,7 +19783,7 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
@@ -19469,7 +19791,7 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -19477,7 +19799,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
@@ -19485,7 +19807,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -19493,7 +19815,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
@@ -19501,7 +19823,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
@@ -19509,7 +19831,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -19517,7 +19839,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -19525,7 +19847,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
@@ -19533,7 +19855,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
@@ -19541,7 +19863,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
@@ -19549,7 +19871,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -19557,7 +19879,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
@@ -19565,7 +19887,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
@@ -19573,7 +19895,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
@@ -19581,7 +19903,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
@@ -19589,7 +19911,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
@@ -19597,7 +19919,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
@@ -19605,7 +19927,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
@@ -19613,7 +19935,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
@@ -19621,7 +19943,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
@@ -19629,7 +19951,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
@@ -19637,7 +19959,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -19645,7 +19967,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
@@ -19653,7 +19975,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
@@ -19661,7 +19983,7 @@
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -19669,7 +19991,7 @@
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -19677,7 +19999,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
@@ -19685,7 +20007,7 @@
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -19693,7 +20015,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -19701,7 +20023,7 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
@@ -19709,7 +20031,7 @@
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
@@ -19717,7 +20039,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
@@ -19725,7 +20047,7 @@
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
@@ -19733,7 +20055,7 @@
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
@@ -19741,7 +20063,7 @@
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
@@ -19749,7 +20071,7 @@
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
     </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
@@ -19757,7 +20079,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
@@ -19765,7 +20087,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -19773,7 +20095,7 @@
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
@@ -19781,7 +20103,7 @@
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
@@ -19789,7 +20111,7 @@
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
@@ -19797,7 +20119,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
@@ -19805,7 +20127,7 @@
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
     </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -19813,7 +20135,7 @@
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -19821,7 +20143,7 @@
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
@@ -19829,7 +20151,7 @@
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
@@ -19837,7 +20159,7 @@
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
@@ -19845,7 +20167,7 @@
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
@@ -19853,7 +20175,7 @@
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
@@ -19861,7 +20183,7 @@
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
     </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
@@ -19869,7 +20191,7 @@
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
     </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
@@ -19877,7 +20199,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
@@ -19885,7 +20207,7 @@
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
@@ -19893,7 +20215,7 @@
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
@@ -19901,7 +20223,7 @@
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
     </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
@@ -19909,7 +20231,7 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
     </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
@@ -19917,7 +20239,7 @@
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
@@ -19925,7 +20247,7 @@
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
     </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
@@ -19933,7 +20255,7 @@
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
     </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
@@ -19941,7 +20263,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -19949,7 +20271,7 @@
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
     </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
@@ -19957,7 +20279,7 @@
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
     </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
@@ -19965,7 +20287,7 @@
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
     </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
@@ -19973,7 +20295,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
@@ -19981,7 +20303,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
@@ -19989,7 +20311,7 @@
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
     </row>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
@@ -19997,7 +20319,7 @@
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
     </row>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -20005,7 +20327,7 @@
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
@@ -20013,7 +20335,7 @@
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
     </row>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
@@ -20021,7 +20343,7 @@
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
     </row>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
@@ -20029,7 +20351,7 @@
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
     </row>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -20037,7 +20359,7 @@
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
     </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
@@ -20045,7 +20367,7 @@
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
     </row>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
@@ -20053,7 +20375,7 @@
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
     </row>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
@@ -20061,7 +20383,7 @@
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
     </row>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
@@ -20069,7 +20391,7 @@
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
     </row>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -20077,7 +20399,7 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -20085,7 +20407,7 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
@@ -20093,7 +20415,7 @@
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
     </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
@@ -20101,7 +20423,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
@@ -20109,7 +20431,7 @@
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
@@ -20117,7 +20439,7 @@
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
@@ -20125,7 +20447,7 @@
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
@@ -20133,7 +20455,7 @@
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
@@ -20141,7 +20463,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
@@ -20149,7 +20471,7 @@
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
@@ -20157,7 +20479,7 @@
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
@@ -20165,7 +20487,7 @@
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
@@ -20173,7 +20495,7 @@
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
@@ -20181,7 +20503,7 @@
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
@@ -20189,7 +20511,7 @@
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
@@ -20197,7 +20519,7 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -20205,7 +20527,7 @@
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
@@ -20213,7 +20535,7 @@
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
@@ -20221,7 +20543,7 @@
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
@@ -20229,7 +20551,7 @@
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
@@ -20237,7 +20559,7 @@
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
@@ -20245,7 +20567,7 @@
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
@@ -20253,7 +20575,7 @@
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
@@ -20261,7 +20583,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
@@ -20269,7 +20591,7 @@
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
@@ -20277,7 +20599,7 @@
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
@@ -20285,7 +20607,7 @@
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
@@ -20293,7 +20615,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
@@ -20301,7 +20623,7 @@
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
@@ -20309,7 +20631,7 @@
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
@@ -20317,7 +20639,7 @@
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
@@ -20325,7 +20647,7 @@
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
@@ -20333,7 +20655,7 @@
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
@@ -20341,7 +20663,7 @@
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
@@ -20349,7 +20671,7 @@
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
@@ -20357,1064 +20679,1064 @@
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
     </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
     </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
     </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
     </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
     </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
     </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
     </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
     </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
     </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
     </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
     </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
     </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
     </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
     </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
     </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
     </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
     </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
     </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
     </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
     </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
     </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
     </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
     </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
     </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
     </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
     </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
     </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
     </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
     </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
     </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
     </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
     </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
     </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
     </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
     </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
     </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
     </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
     </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
     </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
     </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
     </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
     </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
     </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
     </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
     </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
     </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
     </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
     </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
     </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
     </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
     </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
     </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
     </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
     </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
     </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
     </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
     </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
     </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
     </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
     </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
     </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
     </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
     </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
     </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
     </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
     </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
     </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
     </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
     </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
     </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
     </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
     </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
     </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
     </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
     </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
     </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
     </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
     </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
     </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
     </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
     </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
     </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
     </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
     </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
     </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
     </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
     </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
     </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
     </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
     </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
     </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
     </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
     </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
     </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
     </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
     </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
     </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
     </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
     </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
     </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
     </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
     </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
     </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
     </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
     </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
     </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
     </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
     </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
     </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
     </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
     </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
     </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
     </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
     </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
     </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
     </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
     </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
     </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
     </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="353" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
     </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
     </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
     </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
     </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
     </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
     </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
     </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="362" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
     </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.35">
+    <row r="363" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -21430,9 +21752,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
@@ -21458,7 +21780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>50</v>
       </c>
@@ -21484,7 +21806,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>54</v>
       </c>
@@ -21510,7 +21832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>56</v>
       </c>
@@ -21536,7 +21858,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>58</v>
       </c>
@@ -21562,7 +21884,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>60</v>
       </c>
@@ -21588,7 +21910,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="s">
         <v>62</v>
       </c>
@@ -21614,7 +21936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>63</v>
       </c>
@@ -21640,7 +21962,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
@@ -21666,7 +21988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
@@ -21692,7 +22014,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>66</v>
       </c>
@@ -21718,7 +22040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>67</v>
       </c>
@@ -21744,7 +22066,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>69</v>
       </c>
@@ -21770,7 +22092,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
         <v>70</v>
       </c>
@@ -21796,7 +22118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
@@ -21822,7 +22144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>72</v>
       </c>
@@ -21848,7 +22170,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>73</v>
       </c>
@@ -21874,7 +22196,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>74</v>
       </c>
@@ -21900,7 +22222,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
@@ -21926,7 +22248,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
         <v>76</v>
       </c>
@@ -21952,7 +22274,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
@@ -21978,7 +22300,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
@@ -22004,7 +22326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>39</v>
       </c>
@@ -22030,7 +22352,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -22056,7 +22378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>41</v>
       </c>
@@ -22082,7 +22404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
@@ -22108,7 +22430,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>79</v>
       </c>
@@ -22134,7 +22456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>81</v>
       </c>
@@ -22160,7 +22482,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>82</v>
       </c>
@@ -22186,7 +22508,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>83</v>
       </c>
@@ -22212,7 +22534,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="s">
         <v>84</v>
       </c>
@@ -22238,7 +22560,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
         <v>85</v>
       </c>
@@ -22272,12 +22594,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="37" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -22294,7 +22616,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -22311,7 +22633,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -22328,7 +22650,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -22345,7 +22667,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -22362,7 +22684,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -22379,7 +22701,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -22404,9 +22726,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>100</v>
       </c>
@@ -22426,7 +22748,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -22446,7 +22768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -22466,12 +22788,12 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>102</v>
       </c>
-      <c r="B4">
-        <v>400000000</v>
+      <c r="B4" s="3">
+        <v>800000000</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -22486,7 +22808,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -22506,7 +22828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -22526,12 +22848,12 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>103</v>
       </c>
-      <c r="B7">
-        <v>400000000</v>
+      <c r="B7" s="3">
+        <v>800000000</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -22546,7 +22868,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -22566,7 +22888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -22586,12 +22908,12 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>104</v>
       </c>
-      <c r="B10">
-        <v>400000000</v>
+      <c r="B10" s="3">
+        <v>800000000</v>
       </c>
       <c r="C10">
         <v>12</v>
@@ -22606,7 +22928,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>105</v>
       </c>
@@ -22626,7 +22948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>105</v>
       </c>
@@ -22646,12 +22968,12 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>105</v>
       </c>
-      <c r="B13">
-        <v>400000000</v>
+      <c r="B13" s="3">
+        <v>800000000</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -22666,7 +22988,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -22686,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -22706,12 +23028,12 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>106</v>
       </c>
-      <c r="B16">
-        <v>400000000</v>
+      <c r="B16" s="3">
+        <v>800000000</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -22734,9 +23056,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -22774,194 +23096,194 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>-0.02</v>
-      </c>
-      <c r="D2">
-        <v>-0.2</v>
-      </c>
-      <c r="E2">
-        <v>-1</v>
-      </c>
-      <c r="F2">
-        <v>-2</v>
-      </c>
-      <c r="G2">
-        <v>-3</v>
-      </c>
-      <c r="H2">
-        <v>-5</v>
-      </c>
-      <c r="I2">
-        <v>-10</v>
-      </c>
-      <c r="J2">
-        <v>-20</v>
-      </c>
-      <c r="K2">
-        <v>-40</v>
-      </c>
-      <c r="L2">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C2" s="4">
+        <v>-200</v>
+      </c>
+      <c r="D2" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="F2" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="G2" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="H2" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="I2" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="J2" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="K2" s="4">
+        <v>-2400000</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-4800000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>103</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>0</v>
       </c>
-      <c r="C3">
-        <v>-0.02</v>
-      </c>
-      <c r="D3">
-        <v>-0.2</v>
-      </c>
-      <c r="E3">
-        <v>-1</v>
-      </c>
-      <c r="F3">
-        <v>-2</v>
-      </c>
-      <c r="G3">
-        <v>-3</v>
-      </c>
-      <c r="H3">
-        <v>-5</v>
-      </c>
-      <c r="I3">
-        <v>-10</v>
-      </c>
-      <c r="J3">
-        <v>-20</v>
-      </c>
-      <c r="K3">
-        <v>-40</v>
-      </c>
-      <c r="L3">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C3" s="4">
+        <v>-200</v>
+      </c>
+      <c r="D3" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="F3" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="G3" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="H3" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="I3" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="J3" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="K3" s="4">
+        <v>-2400000</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-4800000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>0</v>
       </c>
-      <c r="C4">
-        <v>-0.02</v>
-      </c>
-      <c r="D4">
-        <v>-0.2</v>
-      </c>
-      <c r="E4">
-        <v>-1</v>
-      </c>
-      <c r="F4">
-        <v>-2</v>
-      </c>
-      <c r="G4">
-        <v>-3</v>
-      </c>
-      <c r="H4">
-        <v>-5</v>
-      </c>
-      <c r="I4">
-        <v>-10</v>
-      </c>
-      <c r="J4">
-        <v>-20</v>
-      </c>
-      <c r="K4">
-        <v>-40</v>
-      </c>
-      <c r="L4">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C4" s="4">
+        <v>-200</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="F4" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="G4" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="H4" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="I4" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="J4" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="K4" s="4">
+        <v>-2400000</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-4800000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>105</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>-0.02</v>
-      </c>
-      <c r="D5">
-        <v>-0.2</v>
-      </c>
-      <c r="E5">
-        <v>-1</v>
-      </c>
-      <c r="F5">
-        <v>-2</v>
-      </c>
-      <c r="G5">
-        <v>-3</v>
-      </c>
-      <c r="H5">
-        <v>-5</v>
-      </c>
-      <c r="I5">
-        <v>-10</v>
-      </c>
-      <c r="J5">
-        <v>-20</v>
-      </c>
-      <c r="K5">
-        <v>-40</v>
-      </c>
-      <c r="L5">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C5" s="4">
+        <v>-200</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="F5" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="H5" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="J5" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="K5" s="4">
+        <v>-2400000</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-4800000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>106</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>0</v>
       </c>
-      <c r="C6">
-        <v>-0.02</v>
-      </c>
-      <c r="D6">
-        <v>-0.2</v>
-      </c>
-      <c r="E6">
-        <v>-1</v>
-      </c>
-      <c r="F6">
-        <v>-2</v>
-      </c>
-      <c r="G6">
-        <v>-3</v>
-      </c>
-      <c r="H6">
-        <v>-5</v>
-      </c>
-      <c r="I6">
-        <v>-10</v>
-      </c>
-      <c r="J6">
-        <v>-20</v>
-      </c>
-      <c r="K6">
-        <v>-40</v>
-      </c>
-      <c r="L6">
-        <v>-60</v>
+      <c r="C6" s="4">
+        <v>-200</v>
+      </c>
+      <c r="D6" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="F6" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="H6" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="I6" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="J6" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="K6" s="4">
+        <v>-2400000</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-4800000</v>
       </c>
     </row>
   </sheetData>
@@ -22972,13 +23294,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="10.90625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.9296875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.9296875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -23020,7 +23342,7 @@
       </c>
       <c r="N1" s="4"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -23062,7 +23384,7 @@
       </c>
       <c r="N2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -23104,12 +23426,12 @@
       </c>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>102</v>
       </c>
-      <c r="B4">
-        <v>400000000</v>
+      <c r="B4" s="3">
+        <v>800000000</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -23146,7 +23468,7 @@
       </c>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -23188,7 +23510,7 @@
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -23230,12 +23552,12 @@
       </c>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>103</v>
       </c>
-      <c r="B7">
-        <v>400000000</v>
+      <c r="B7" s="3">
+        <v>800000000</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -23272,7 +23594,7 @@
       </c>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -23314,7 +23636,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -23356,12 +23678,12 @@
       </c>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>104</v>
       </c>
-      <c r="B10">
-        <v>400000000</v>
+      <c r="B10" s="3">
+        <v>800000000</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -23398,7 +23720,7 @@
       </c>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>105</v>
       </c>
@@ -23440,7 +23762,7 @@
       </c>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>105</v>
       </c>
@@ -23482,12 +23804,12 @@
       </c>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>105</v>
       </c>
-      <c r="B13">
-        <v>400000000</v>
+      <c r="B13" s="3">
+        <v>800000000</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -23524,7 +23846,7 @@
       </c>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -23566,7 +23888,7 @@
       </c>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -23608,12 +23930,12 @@
       </c>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>106</v>
       </c>
-      <c r="B16">
-        <v>400000000</v>
+      <c r="B16" s="3">
+        <v>800000000</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -23650,10 +23972,10 @@
       </c>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.45">
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -23671,7 +23993,7 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -23684,7 +24006,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -23697,7 +24019,7 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -23712,7 +24034,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -23725,7 +24047,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -23738,7 +24060,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -23753,7 +24075,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -23766,7 +24088,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -23779,7 +24101,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -23794,7 +24116,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -23807,7 +24129,7 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -23820,7 +24142,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -23833,7 +24155,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -23846,7 +24168,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.45">
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -23859,11 +24181,11 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D33" s="3"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -23876,39 +24198,39 @@
       <c r="M34" s="3"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D35" s="3"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D36" s="3"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D45" s="3"/>
     </row>
   </sheetData>

--- a/assets/3D/setup.xlsx
+++ b/assets/3D/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\assets\3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DA9850-94A6-4A8F-8EDD-5711DAF71260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05EA8D0-995C-4015-A8D7-B23A07312039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="11483" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1196">
   <si>
     <t>nlay</t>
   </si>
@@ -3565,6 +3565,75 @@
   </si>
   <si>
     <t>kv_1E-07_kh_1E-03</t>
+  </si>
+  <si>
+    <t>Run01</t>
+  </si>
+  <si>
+    <t>Run02</t>
+  </si>
+  <si>
+    <t>kv_1E-12_kh_1E-07</t>
+  </si>
+  <si>
+    <t>kv_1E-12_kh_1E-06</t>
+  </si>
+  <si>
+    <t>kv_1E-12_kh_1E-05</t>
+  </si>
+  <si>
+    <t>kv_1E-12_kh_1E-04</t>
+  </si>
+  <si>
+    <t>kv_1E-12_kh_1E-03</t>
+  </si>
+  <si>
+    <t>kv_1E-10_kh_1E-07</t>
+  </si>
+  <si>
+    <t>kv_1E-10_kh_1E-06</t>
+  </si>
+  <si>
+    <t>kv_1E-10_kh_1E-05</t>
+  </si>
+  <si>
+    <t>kv_1E-10_kh_1E-04</t>
+  </si>
+  <si>
+    <t>kv_1E-10_kh_1E-03</t>
+  </si>
+  <si>
+    <t>kv_1E-08_kh_1E-07</t>
+  </si>
+  <si>
+    <t>kv_1E-08_kh_1E-06</t>
+  </si>
+  <si>
+    <t>kv_1E-08_kh_1E-05</t>
+  </si>
+  <si>
+    <t>kv_1E-08_kh_1E-04</t>
+  </si>
+  <si>
+    <t>kv_1E-08_kh_1E-03</t>
+  </si>
+  <si>
+    <t>kv_1E-06_kh_1E-07</t>
+  </si>
+  <si>
+    <t>kv_1E-06_kh_1E-06</t>
+  </si>
+  <si>
+    <t>kv_1E-06_kh_1E-05</t>
+  </si>
+  <si>
+    <t>kv_1E-06_kh_1E-04</t>
+  </si>
+  <si>
+    <t>kv_1E-06_kh_1E-03</t>
+  </si>
+  <si>
+    <t>Run03</t>
   </si>
 </sst>
 </file>
@@ -3621,12 +3690,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -3672,7 +3747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3695,6 +3770,16 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4066,10 +4151,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -4079,7 +4164,7 @@
       <c r="C1" t="s">
         <v>99</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -4103,8 +4188,11 @@
       <c r="K1" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L1" s="4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -4112,34 +4200,37 @@
         <v>0</v>
       </c>
       <c r="C2" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D2" s="4">
+        <v>-50</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F2" s="4">
         <v>-200</v>
       </c>
-      <c r="D2" s="4">
+      <c r="G2" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H2" s="4">
         <v>-2000</v>
       </c>
-      <c r="E2" s="4">
+      <c r="I2" s="4">
         <v>-20000</v>
       </c>
-      <c r="F2" s="4">
+      <c r="J2" s="4">
         <v>-100000</v>
       </c>
-      <c r="G2" s="4">
+      <c r="K2" s="4">
         <v>-200000</v>
       </c>
-      <c r="H2" s="4">
+      <c r="L2" s="4">
         <v>-600000</v>
       </c>
-      <c r="I2" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="J2" s="4">
-        <v>-2400000</v>
-      </c>
-      <c r="K2" s="4">
-        <v>-4800000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -4147,34 +4238,37 @@
         <v>0</v>
       </c>
       <c r="C3" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D3" s="4">
+        <v>-50</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F3" s="4">
         <v>-200</v>
       </c>
-      <c r="D3" s="4">
+      <c r="G3" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H3" s="4">
         <v>-2000</v>
       </c>
-      <c r="E3" s="4">
+      <c r="I3" s="4">
         <v>-20000</v>
       </c>
-      <c r="F3" s="4">
+      <c r="J3" s="4">
         <v>-100000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="K3" s="4">
         <v>-200000</v>
       </c>
-      <c r="H3" s="4">
+      <c r="L3" s="4">
         <v>-600000</v>
       </c>
-      <c r="I3" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="J3" s="4">
-        <v>-2400000</v>
-      </c>
-      <c r="K3" s="4">
-        <v>-4800000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -4182,34 +4276,37 @@
         <v>0</v>
       </c>
       <c r="C4" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-50</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F4" s="4">
         <v>-200</v>
       </c>
-      <c r="D4" s="4">
+      <c r="G4" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H4" s="4">
         <v>-2000</v>
       </c>
-      <c r="E4" s="4">
+      <c r="I4" s="4">
         <v>-20000</v>
       </c>
-      <c r="F4" s="4">
+      <c r="J4" s="4">
         <v>-100000</v>
       </c>
-      <c r="G4" s="4">
+      <c r="K4" s="4">
         <v>-200000</v>
       </c>
-      <c r="H4" s="4">
+      <c r="L4" s="4">
         <v>-600000</v>
       </c>
-      <c r="I4" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="J4" s="4">
-        <v>-2400000</v>
-      </c>
-      <c r="K4" s="4">
-        <v>-4800000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -4217,34 +4314,37 @@
         <v>0</v>
       </c>
       <c r="C5" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-50</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F5" s="4">
         <v>-200</v>
       </c>
-      <c r="D5" s="4">
+      <c r="G5" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H5" s="4">
         <v>-2000</v>
       </c>
-      <c r="E5" s="4">
+      <c r="I5" s="4">
         <v>-20000</v>
       </c>
-      <c r="F5" s="4">
+      <c r="J5" s="4">
         <v>-100000</v>
       </c>
-      <c r="G5" s="4">
+      <c r="K5" s="4">
         <v>-200000</v>
       </c>
-      <c r="H5" s="4">
+      <c r="L5" s="4">
         <v>-600000</v>
       </c>
-      <c r="I5" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="J5" s="4">
-        <v>-2400000</v>
-      </c>
-      <c r="K5" s="4">
-        <v>-4800000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -4252,31 +4352,34 @@
         <v>0</v>
       </c>
       <c r="C6" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D6" s="4">
+        <v>-50</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F6" s="4">
         <v>-200</v>
       </c>
-      <c r="D6" s="4">
+      <c r="G6" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H6" s="4">
         <v>-2000</v>
       </c>
-      <c r="E6" s="4">
+      <c r="I6" s="4">
         <v>-20000</v>
       </c>
-      <c r="F6" s="4">
+      <c r="J6" s="4">
         <v>-100000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="K6" s="4">
         <v>-200000</v>
       </c>
-      <c r="H6" s="4">
+      <c r="L6" s="4">
         <v>-600000</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="J6" s="4">
-        <v>-2400000</v>
-      </c>
-      <c r="K6" s="4">
-        <v>-4800000</v>
       </c>
     </row>
   </sheetData>
@@ -4291,18 +4394,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="4" width="10.9296875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="4"/>
+    <col min="6" max="6" width="10.59765625" style="4"/>
     <col min="10" max="10" width="10.9296875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -4337,19 +4440,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>0</v>
       </c>
       <c r="F2" s="4">
@@ -4378,95 +4481,95 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="3">
         <v>3600000</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>0</v>
       </c>
       <c r="D3" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F3" s="4">
         <v>-100</v>
       </c>
-      <c r="E3">
+      <c r="G3" s="4">
         <v>-200</v>
       </c>
-      <c r="F3" s="4">
+      <c r="H3" s="4">
         <v>-1000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="I3" s="4">
         <v>-2000</v>
       </c>
-      <c r="H3" s="4">
+      <c r="J3" s="4">
         <v>-20000</v>
       </c>
-      <c r="I3" s="4">
+      <c r="K3" s="4">
         <v>-100000</v>
       </c>
-      <c r="J3" s="4">
+      <c r="L3" s="4">
         <v>-200000</v>
       </c>
-      <c r="K3" s="4">
+      <c r="M3" s="4">
         <v>-600000</v>
       </c>
-      <c r="L3" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M3" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B4" s="3">
         <v>800000000</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F4" s="4">
         <v>-100</v>
       </c>
-      <c r="E4">
+      <c r="G4" s="4">
         <v>-200</v>
       </c>
-      <c r="F4" s="4">
+      <c r="H4" s="4">
         <v>-1000</v>
       </c>
-      <c r="G4" s="4">
+      <c r="I4" s="4">
         <v>-2000</v>
       </c>
-      <c r="H4" s="4">
+      <c r="J4" s="4">
         <v>-20000</v>
       </c>
-      <c r="I4" s="4">
+      <c r="K4" s="4">
         <v>-100000</v>
       </c>
-      <c r="J4" s="4">
+      <c r="L4" s="4">
         <v>-200000</v>
       </c>
-      <c r="K4" s="4">
+      <c r="M4" s="4">
         <v>-600000</v>
       </c>
-      <c r="L4" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M4" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5" s="4">
@@ -4501,95 +4604,95 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B6" s="3">
         <v>3600000</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F6" s="4">
         <v>-100</v>
       </c>
-      <c r="E6" s="4">
+      <c r="G6" s="4">
         <v>-200</v>
       </c>
-      <c r="F6" s="4">
+      <c r="H6" s="4">
         <v>-1000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="I6" s="4">
         <v>-2000</v>
       </c>
-      <c r="H6" s="4">
+      <c r="J6" s="4">
         <v>-20000</v>
       </c>
-      <c r="I6" s="4">
+      <c r="K6" s="4">
         <v>-100000</v>
       </c>
-      <c r="J6" s="4">
+      <c r="L6" s="4">
         <v>-200000</v>
       </c>
-      <c r="K6" s="4">
+      <c r="M6" s="4">
         <v>-600000</v>
       </c>
-      <c r="L6" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M6" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B7" s="3">
         <v>800000000</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>0</v>
       </c>
       <c r="D7" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E7" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F7" s="4">
         <v>-100</v>
       </c>
-      <c r="E7" s="4">
+      <c r="G7" s="4">
         <v>-200</v>
       </c>
-      <c r="F7" s="4">
+      <c r="H7" s="4">
         <v>-1000</v>
       </c>
-      <c r="G7" s="4">
+      <c r="I7" s="4">
         <v>-2000</v>
       </c>
-      <c r="H7" s="4">
+      <c r="J7" s="4">
         <v>-20000</v>
       </c>
-      <c r="I7" s="4">
+      <c r="K7" s="4">
         <v>-100000</v>
       </c>
-      <c r="J7" s="4">
+      <c r="L7" s="4">
         <v>-200000</v>
       </c>
-      <c r="K7" s="4">
+      <c r="M7" s="4">
         <v>-600000</v>
       </c>
-      <c r="L7" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M7" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>0</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -4624,95 +4727,95 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B9" s="3">
         <v>3600000</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E9" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F9" s="4">
         <v>-100</v>
       </c>
-      <c r="E9" s="4">
+      <c r="G9" s="4">
         <v>-200</v>
       </c>
-      <c r="F9" s="4">
+      <c r="H9" s="4">
         <v>-1000</v>
       </c>
-      <c r="G9" s="4">
+      <c r="I9" s="4">
         <v>-2000</v>
       </c>
-      <c r="H9" s="4">
+      <c r="J9" s="4">
         <v>-20000</v>
       </c>
-      <c r="I9" s="4">
+      <c r="K9" s="4">
         <v>-100000</v>
       </c>
-      <c r="J9" s="4">
+      <c r="L9" s="4">
         <v>-200000</v>
       </c>
-      <c r="K9" s="4">
+      <c r="M9" s="4">
         <v>-600000</v>
       </c>
-      <c r="L9" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M9" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B10" s="3">
         <v>800000000</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E10" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F10" s="4">
         <v>-100</v>
       </c>
-      <c r="E10" s="4">
+      <c r="G10" s="4">
         <v>-200</v>
       </c>
-      <c r="F10" s="4">
+      <c r="H10" s="4">
         <v>-1000</v>
       </c>
-      <c r="G10" s="4">
+      <c r="I10" s="4">
         <v>-2000</v>
       </c>
-      <c r="H10" s="4">
+      <c r="J10" s="4">
         <v>-20000</v>
       </c>
-      <c r="I10" s="4">
+      <c r="K10" s="4">
         <v>-100000</v>
       </c>
-      <c r="J10" s="4">
+      <c r="L10" s="4">
         <v>-200000</v>
       </c>
-      <c r="K10" s="4">
+      <c r="M10" s="4">
         <v>-600000</v>
       </c>
-      <c r="L10" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M10" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>0</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>0</v>
       </c>
       <c r="D11" s="4">
@@ -4747,95 +4850,95 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B12" s="3">
         <v>3600000</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>0</v>
       </c>
       <c r="D12" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E12" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F12" s="4">
         <v>-100</v>
       </c>
-      <c r="E12" s="4">
+      <c r="G12" s="4">
         <v>-200</v>
       </c>
-      <c r="F12" s="4">
+      <c r="H12" s="4">
         <v>-1000</v>
       </c>
-      <c r="G12" s="4">
+      <c r="I12" s="4">
         <v>-2000</v>
       </c>
-      <c r="H12" s="4">
+      <c r="J12" s="4">
         <v>-20000</v>
       </c>
-      <c r="I12" s="4">
+      <c r="K12" s="4">
         <v>-100000</v>
       </c>
-      <c r="J12" s="4">
+      <c r="L12" s="4">
         <v>-200000</v>
       </c>
-      <c r="K12" s="4">
+      <c r="M12" s="4">
         <v>-600000</v>
       </c>
-      <c r="L12" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M12" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="3">
         <v>800000000</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>0</v>
       </c>
       <c r="D13" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E13" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F13" s="4">
         <v>-100</v>
       </c>
-      <c r="E13" s="4">
+      <c r="G13" s="4">
         <v>-200</v>
       </c>
-      <c r="F13" s="4">
+      <c r="H13" s="4">
         <v>-1000</v>
       </c>
-      <c r="G13" s="4">
+      <c r="I13" s="4">
         <v>-2000</v>
       </c>
-      <c r="H13" s="4">
+      <c r="J13" s="4">
         <v>-20000</v>
       </c>
-      <c r="I13" s="4">
+      <c r="K13" s="4">
         <v>-100000</v>
       </c>
-      <c r="J13" s="4">
+      <c r="L13" s="4">
         <v>-200000</v>
       </c>
-      <c r="K13" s="4">
+      <c r="M13" s="4">
         <v>-600000</v>
       </c>
-      <c r="L13" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M13" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>0</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>0</v>
       </c>
       <c r="D14" s="4">
@@ -4870,85 +4973,85 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="3">
         <v>3600000</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>0</v>
       </c>
       <c r="D15" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E15" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F15" s="4">
         <v>-100</v>
       </c>
-      <c r="E15" s="4">
+      <c r="G15" s="4">
         <v>-200</v>
       </c>
-      <c r="F15" s="4">
+      <c r="H15" s="4">
         <v>-1000</v>
       </c>
-      <c r="G15" s="4">
+      <c r="I15" s="4">
         <v>-2000</v>
       </c>
-      <c r="H15" s="4">
+      <c r="J15" s="4">
         <v>-20000</v>
       </c>
-      <c r="I15" s="4">
+      <c r="K15" s="4">
         <v>-100000</v>
       </c>
-      <c r="J15" s="4">
+      <c r="L15" s="4">
         <v>-200000</v>
       </c>
-      <c r="K15" s="4">
+      <c r="M15" s="4">
         <v>-600000</v>
       </c>
-      <c r="L15" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M15" s="4">
-        <v>-2400000</v>
-      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="A16" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B16" s="3">
         <v>800000000</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>0</v>
       </c>
       <c r="D16" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E16" s="4">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="4">
         <v>-100</v>
       </c>
-      <c r="E16" s="4">
+      <c r="G16" s="4">
         <v>-200</v>
       </c>
-      <c r="F16" s="4">
+      <c r="H16" s="4">
         <v>-1000</v>
       </c>
-      <c r="G16" s="4">
+      <c r="I16" s="4">
         <v>-2000</v>
       </c>
-      <c r="H16" s="4">
+      <c r="J16" s="4">
         <v>-20000</v>
       </c>
-      <c r="I16" s="4">
+      <c r="K16" s="4">
         <v>-100000</v>
       </c>
-      <c r="J16" s="4">
+      <c r="L16" s="4">
         <v>-200000</v>
       </c>
-      <c r="K16" s="4">
+      <c r="M16" s="4">
         <v>-600000</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-1200000</v>
-      </c>
-      <c r="M16" s="4">
-        <v>-2400000</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -5198,7 +5301,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -5217,50 +5320,40 @@
         <v>1157</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>1160</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>1161</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>1163</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1164</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>1165</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>1170</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>1171</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>1172</v>
-      </c>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
@@ -5331,21 +5424,11 @@
       <c r="P2" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q2" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U2" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -5386,51 +5469,41 @@
       <c r="F3" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="H3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="I3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="J3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="K3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="L3" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="H3" s="13">
+      <c r="M3" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="I3" s="13">
+      <c r="N3" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="J3" s="13">
+      <c r="O3" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="K3" s="13">
+      <c r="P3" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="L3" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="M3" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="N3" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="O3" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="P3" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R3" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S3" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T3" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U3" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -5501,21 +5574,11 @@
       <c r="P4" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q4" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U4" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -5556,51 +5619,41 @@
       <c r="F5" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="H5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="I5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="J5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="K5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="L5" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="H5" s="13">
+      <c r="M5" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="I5" s="13">
+      <c r="N5" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="J5" s="13">
+      <c r="O5" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="K5" s="13">
+      <c r="P5" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="L5" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="M5" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="N5" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="O5" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="P5" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R5" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S5" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T5" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U5" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
@@ -5671,21 +5724,11 @@
       <c r="P6" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q6" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U6" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -5756,21 +5799,11 @@
       <c r="P7" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q7" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U7" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -5811,51 +5844,41 @@
       <c r="F8" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="H8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="I8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="J8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="K8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="L8" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="H8" s="13">
+      <c r="M8" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="I8" s="13">
+      <c r="N8" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="J8" s="13">
+      <c r="O8" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="K8" s="13">
+      <c r="P8" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="L8" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="M8" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="N8" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="O8" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="P8" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R8" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S8" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T8" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U8" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -5926,21 +5949,11 @@
       <c r="P9" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q9" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U9" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -5981,51 +5994,41 @@
       <c r="F10" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="H10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="I10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="J10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="K10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="L10" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="H10" s="13">
+      <c r="M10" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="I10" s="13">
+      <c r="N10" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="J10" s="13">
+      <c r="O10" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="K10" s="13">
+      <c r="P10" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="L10" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="M10" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="N10" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="O10" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="P10" s="13">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R10" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S10" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T10" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U10" s="13">
-        <v>8.6400000000000001E-3</v>
-      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
@@ -6096,21 +6099,11 @@
       <c r="P11" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q11" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="U11" s="1">
-        <v>86.4</v>
-      </c>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -6141,10 +6134,11 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:BB364"/>
+  <dimension ref="A1:BO364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
@@ -12058,7 +12052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>200</v>
       </c>
@@ -12151,7 +12145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>201</v>
       </c>
@@ -12256,7 +12250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>202</v>
       </c>
@@ -12362,7 +12356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>203</v>
       </c>
@@ -12468,7 +12462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>204</v>
       </c>
@@ -12541,7 +12535,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="86" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>205</v>
       </c>
@@ -12614,7 +12608,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="87" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>206</v>
       </c>
@@ -12687,7 +12681,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="88" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>207</v>
       </c>
@@ -12741,7 +12735,7 @@
         <v>6.7755654381398901E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:54" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>208</v>
       </c>
@@ -12794,8 +12788,11 @@
         <f t="shared" si="11"/>
         <v>9.4339543613295384E-4</v>
       </c>
-    </row>
-    <row r="90" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="BC89" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="90" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -12848,8 +12845,50 @@
         <f t="shared" si="11"/>
         <v>5.8085408169564559E-4</v>
       </c>
-    </row>
-    <row r="91" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE90" t="s">
+        <v>1173</v>
+      </c>
+      <c r="BC90" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD90" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BE90" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF90" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH90" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI90" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ90" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK90" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL90" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM90" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN90" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO90" s="4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="91" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>210</v>
       </c>
@@ -12902,8 +12941,110 @@
         <f t="shared" si="11"/>
         <v>3.6120501290660029E-4</v>
       </c>
-    </row>
-    <row r="92" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE91" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF91" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AG91" s="16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AH91" s="16" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AI91" s="16" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AJ91" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AK91" s="16" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AL91" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AM91" s="16" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN91" s="16" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AO91" s="16" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AP91" s="19" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AQ91" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AR91" s="19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AS91" s="19" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AT91" s="19" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AU91" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AV91" s="19" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AW91" s="19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AX91" s="19" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AY91" s="19" t="s">
+        <v>1172</v>
+      </c>
+      <c r="BC91" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>211</v>
       </c>
@@ -12956,8 +13097,110 @@
         <f t="shared" si="11"/>
         <v>6.2975536923403231E-4</v>
       </c>
-    </row>
-    <row r="93" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE92" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF92" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG92" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH92" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI92" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ92" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK92" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL92" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM92" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN92" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO92" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP92" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ92" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR92" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS92" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT92" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU92" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV92" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW92" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX92" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY92" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC92" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD92" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE92" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF92" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG92" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH92" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI92" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ92" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK92" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL92" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM92" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN92" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO92" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>212</v>
       </c>
@@ -13010,8 +13253,110 @@
         <f t="shared" si="11"/>
         <v>7.228323272845125E-4</v>
       </c>
-    </row>
-    <row r="94" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE93" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF93" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG93" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH93" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI93" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ93" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK93" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AL93" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AM93" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AN93" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AO93" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AP93" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AQ93" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AR93" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AS93" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AT93" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AU93" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV93" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW93" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX93" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY93" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="BC93" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD93" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE93" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF93" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG93" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH93" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI93" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ93" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK93" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL93" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM93" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN93" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO93" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>213</v>
       </c>
@@ -13064,8 +13409,110 @@
         <f t="shared" si="11"/>
         <v>4.6803677487896461E-4</v>
       </c>
-    </row>
-    <row r="95" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE94" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF94" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG94" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH94" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI94" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ94" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK94" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL94" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM94" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN94" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO94" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP94" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ94" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR94" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS94" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT94" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU94" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV94" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW94" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX94" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY94" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC94" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>214</v>
       </c>
@@ -13118,8 +13565,110 @@
         <f t="shared" si="11"/>
         <v>7.7336905885629418E-4</v>
       </c>
-    </row>
-    <row r="96" spans="1:54" x14ac:dyDescent="0.45">
+      <c r="AE95" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF95" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG95" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH95" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI95" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ95" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK95" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AL95" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AM95" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AN95" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AO95" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AP95" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AQ95" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AR95" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AS95" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AT95" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AU95" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV95" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW95" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX95" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY95" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="BC95" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD95" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE95" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF95" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG95" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH95" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI95" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ95" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK95" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL95" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM95" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN95" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO95" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>215</v>
       </c>
@@ -13172,8 +13721,110 @@
         <f t="shared" si="11"/>
         <v>5.6237098746364077E-4</v>
       </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE96" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF96" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG96" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH96" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI96" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ96" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK96" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL96" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM96" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN96" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO96" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP96" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ96" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR96" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS96" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT96" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU96" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV96" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW96" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX96" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY96" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC96" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD96" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE96" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF96" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG96" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH96" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI96" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ96" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK96" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL96" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM96" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN96" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO96" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -13226,8 +13877,110 @@
         <f t="shared" si="11"/>
         <v>8.1362777910270177E-4</v>
       </c>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE97" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF97" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG97" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH97" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI97" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ97" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK97" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL97" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM97" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN97" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO97" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP97" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ97" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR97" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS97" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT97" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU97" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV97" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW97" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX97" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY97" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>217</v>
       </c>
@@ -13280,8 +14033,110 @@
         <f t="shared" ref="AA98:AA129" si="15">+W98</f>
         <v>4.356087488178263E-4</v>
       </c>
-    </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE98" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF98" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG98" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH98" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI98" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ98" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK98" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AL98" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AM98" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AN98" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AO98" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AP98" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AQ98" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AR98" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AS98" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AT98" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AU98" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV98" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW98" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX98" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY98" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="BC98" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD98" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE98" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF98" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG98" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH98" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI98" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ98" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK98" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL98" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM98" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN98" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO98" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>218</v>
       </c>
@@ -13334,8 +14189,110 @@
         <f t="shared" si="15"/>
         <v>1.0028195602172999E-3</v>
       </c>
-    </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE99" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF99" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG99" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH99" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI99" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ99" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK99" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL99" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM99" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN99" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO99" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP99" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ99" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR99" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS99" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT99" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU99" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV99" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW99" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX99" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY99" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC99" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD99" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE99" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF99" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG99" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH99" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI99" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ99" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK99" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL99" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM99" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN99" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO99" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>219</v>
       </c>
@@ -13388,8 +14345,110 @@
         <f t="shared" si="15"/>
         <v>5.0364788225881177E-4</v>
       </c>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE100" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF100" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG100" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH100" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI100" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ100" s="18">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK100" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AL100" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AM100" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AN100" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AO100" s="18">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AP100" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AQ100" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AR100" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AS100" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AT100" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AU100" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV100" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW100" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX100" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY100" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="BC100" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>220</v>
       </c>
@@ -13442,8 +14501,110 @@
         <f t="shared" si="15"/>
         <v>7.9643019829107138E-4</v>
       </c>
-    </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE101" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF101" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG101" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH101" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI101" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AJ101" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AK101" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL101" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM101" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN101" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AO101" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AP101" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ101" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR101" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS101" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AT101" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AU101" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV101" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW101" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX101" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY101" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="BC101" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD101" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE101" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF101" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG101" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH101" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI101" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ101" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK101" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL101" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM101" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN101" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO101" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -13496,8 +14657,47 @@
         <f t="shared" si="15"/>
         <v>4.7180228576033662E-4</v>
       </c>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BC102" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD102" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE102" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF102" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG102" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH102" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI102" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ102" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK102" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL102" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM102" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN102" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO102" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>222</v>
       </c>
@@ -13550,8 +14750,50 @@
         <f t="shared" si="15"/>
         <v>6.1373542849109256E-4</v>
       </c>
-    </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE103" s="14" t="s">
+        <v>1174</v>
+      </c>
+      <c r="BC103" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>223</v>
       </c>
@@ -13604,8 +14846,95 @@
         <f t="shared" si="15"/>
         <v>6.4311012308476624E-4</v>
       </c>
-    </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF104" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AG104" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AH104" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AI104" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AJ104" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AK104" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="AL104" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="AM104" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="AN104" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AO104" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="AP104" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AQ104" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AR104" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AS104" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AT104" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="BC104" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD104" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE104" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF104" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG104" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH104" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI104" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ104" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK104" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL104" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM104" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN104" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO104" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -13658,8 +14987,95 @@
         <f t="shared" si="15"/>
         <v>6.2770310871303756E-4</v>
       </c>
-    </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE105" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF105" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG105" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH105" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI105" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ105" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK105" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL105" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM105" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN105" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO105" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP105" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ105" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR105" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS105" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT105" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC105" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD105" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE105" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF105" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BG105" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BH105" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BI105" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BJ105" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BK105" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BL105" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BM105" s="4">
+        <v>-600000</v>
+      </c>
+      <c r="BN105" s="4">
+        <v>-1200000</v>
+      </c>
+      <c r="BO105" s="4">
+        <v>-2400000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -13712,8 +15128,56 @@
         <f t="shared" si="15"/>
         <v>5.7559569640524308E-4</v>
       </c>
-    </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE106" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF106" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG106" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH106" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI106" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ106" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK106" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AL106" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AM106" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AN106" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AO106" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AP106" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AQ106" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AR106" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AS106" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AT106" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -13766,8 +15230,56 @@
         <f t="shared" si="15"/>
         <v>5.3332641124062639E-4</v>
       </c>
-    </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE107" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF107" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG107" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH107" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI107" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ107" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK107" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL107" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM107" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN107" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO107" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP107" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ107" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR107" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS107" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT107" s="1">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>227</v>
       </c>
@@ -13820,8 +15332,59 @@
         <f t="shared" si="15"/>
         <v>8.2728508003655082E-4</v>
       </c>
-    </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE108" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF108" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG108" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH108" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI108" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ108" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK108" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AL108" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AM108" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AN108" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AO108" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AP108" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AQ108" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AR108" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AS108" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AT108" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="BC108" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="109" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>228</v>
       </c>
@@ -13874,8 +15437,95 @@
         <f t="shared" si="15"/>
         <v>9.7268368705790624E-4</v>
       </c>
-    </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE109" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF109" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG109" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH109" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI109" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ109" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK109" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL109" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM109" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN109" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO109" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP109" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ109" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR109" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS109" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT109" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC109" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD109" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BE109" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF109" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG109" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH109" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI109" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ109" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK109" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL109" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM109" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN109" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO109" s="4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="110" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>229</v>
       </c>
@@ -13928,8 +15578,95 @@
         <f t="shared" si="15"/>
         <v>4.8961483057842047E-4</v>
       </c>
-    </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE110" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF110" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG110" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH110" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI110" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ110" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK110" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL110" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM110" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN110" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO110" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP110" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ110" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR110" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS110" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT110" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC110" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>230</v>
       </c>
@@ -13982,8 +15719,95 @@
         <f t="shared" si="15"/>
         <v>5.6725746685323385E-4</v>
       </c>
-    </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE111" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF111" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG111" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH111" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI111" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ111" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK111" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AL111" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AM111" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AN111" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AO111" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AP111" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AQ111" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AR111" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AS111" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AT111" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="BC111" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD111" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE111" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF111" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG111" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH111" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI111" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ111" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK111" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL111" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM111" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN111" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO111" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>231</v>
       </c>
@@ -14036,8 +15860,95 @@
         <f t="shared" si="15"/>
         <v>5.7586134556664864E-4</v>
       </c>
-    </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE112" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF112" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG112" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH112" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI112" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ112" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK112" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL112" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM112" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN112" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO112" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP112" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ112" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR112" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS112" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT112" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC112" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD112" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE112" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF112" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG112" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH112" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI112" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ112" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK112" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL112" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM112" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN112" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO112" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>232</v>
       </c>
@@ -14090,8 +16001,95 @@
         <f t="shared" si="15"/>
         <v>6.64750588599489E-4</v>
       </c>
-    </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE113" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF113" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG113" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AH113" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AI113" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AJ113" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AK113" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AL113" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AM113" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AN113" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AO113" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="AP113" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AQ113" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AR113" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AS113" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="AT113" s="13">
+        <v>8.6400000000000001E-7</v>
+      </c>
+      <c r="BC113" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -14144,8 +16142,95 @@
         <f t="shared" si="15"/>
         <v>9.4712108096549959E-4</v>
       </c>
-    </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE114" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF114" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG114" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH114" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI114" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ114" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK114" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL114" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM114" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN114" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO114" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP114" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ114" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR114" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS114" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT114" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC114" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD114" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE114" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF114" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG114" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH114" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI114" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ114" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK114" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL114" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM114" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN114" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO114" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -14198,8 +16283,47 @@
         <f t="shared" si="15"/>
         <v>5.5438130895789643E-4</v>
       </c>
-    </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BC115" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD115" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE115" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF115" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG115" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH115" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI115" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ115" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK115" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL115" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM115" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN115" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO115" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>235</v>
       </c>
@@ -14252,8 +16376,55 @@
         <f t="shared" si="15"/>
         <v>9.0184342071178349E-4</v>
       </c>
-    </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE116" s="14" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AF116" s="4"/>
+      <c r="AG116" s="4"/>
+      <c r="AH116" s="4"/>
+      <c r="AI116" s="4"/>
+      <c r="AJ116" s="4"/>
+      <c r="BC116" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO116" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>236</v>
       </c>
@@ -14306,8 +16477,95 @@
         <f t="shared" si="15"/>
         <v>6.2612911789142764E-4</v>
       </c>
-    </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE117" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF117" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AG117" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AH117" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AI117" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AJ117" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AK117" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AL117" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="AM117" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="AN117" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AO117" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AP117" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AQ117" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AR117" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AS117" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AT117" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="BC117" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD117" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE117" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF117" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG117" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH117" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI117" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ117" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK117" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL117" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM117" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN117" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO117" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>237</v>
       </c>
@@ -14360,8 +16618,95 @@
         <f t="shared" si="15"/>
         <v>7.5873173424928584E-4</v>
       </c>
-    </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE118" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF118" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG118" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH118" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI118" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ118" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK118" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL118" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM118" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN118" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO118" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP118" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ118" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR118" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS118" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT118" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC118" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD118" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE118" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF118" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG118" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH118" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI118" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ118" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK118" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL118" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM118" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN118" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO118" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -14414,8 +16759,95 @@
         <f t="shared" si="15"/>
         <v>6.1259290710490542E-4</v>
       </c>
-    </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE119" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF119" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AG119" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AH119" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AI119" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AJ119" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AK119" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AL119" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AM119" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AN119" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AO119" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AP119" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AQ119" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR119" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AS119" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AT119" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="BC119" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -14468,8 +16900,95 @@
         <f t="shared" si="15"/>
         <v>6.9084118394068103E-4</v>
       </c>
-    </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE120" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF120" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG120" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH120" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI120" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ120" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK120" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL120" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM120" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN120" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO120" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP120" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ120" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR120" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS120" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT120" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC120" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD120" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE120" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF120" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG120" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH120" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI120" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ120" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK120" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL120" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM120" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN120" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO120" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -14522,8 +17041,95 @@
         <f t="shared" si="15"/>
         <v>6.6669851278469488E-4</v>
       </c>
-    </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE121" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF121" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AG121" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AH121" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AI121" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AJ121" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AK121" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AL121" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AM121" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AN121" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AO121" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AP121" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AQ121" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR121" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AS121" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AT121" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="BC121" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD121" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF121" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG121" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH121" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI121" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ121" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK121" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL121" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM121" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN121" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO121" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>241</v>
       </c>
@@ -14576,8 +17182,95 @@
         <f t="shared" si="15"/>
         <v>8.2045218583240757E-4</v>
       </c>
-    </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE122" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF122" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG122" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH122" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI122" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ122" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK122" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL122" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM122" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN122" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO122" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP122" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ122" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR122" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS122" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT122" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC122" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>242</v>
       </c>
@@ -14630,8 +17323,95 @@
         <f t="shared" si="15"/>
         <v>5.2081387235738941E-4</v>
       </c>
-    </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE123" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF123" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG123" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH123" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI123" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ123" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK123" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL123" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM123" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN123" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO123" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP123" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ123" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR123" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS123" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT123" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BC123" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD123" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BE123" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF123" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG123" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH123" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI123" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ123" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK123" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL123" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM123" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN123" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO123" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>243</v>
       </c>
@@ -14684,8 +17464,95 @@
         <f t="shared" si="15"/>
         <v>5.7189465431413248E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE124" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF124" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AG124" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AH124" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AI124" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AJ124" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AK124" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AL124" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AM124" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AN124" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AO124" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AP124" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AQ124" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR124" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AS124" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AT124" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="BC124" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD124" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BE124" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF124" s="4">
+        <v>-10</v>
+      </c>
+      <c r="BG124" s="4">
+        <v>-50</v>
+      </c>
+      <c r="BH124" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BI124" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BJ124" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BK124" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BL124" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BM124" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BN124" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BO124" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -14738,8 +17605,56 @@
         <f t="shared" si="15"/>
         <v>9.1233097501937279E-4</v>
       </c>
-    </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE125" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF125" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG125" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH125" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI125" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ125" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK125" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL125" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM125" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN125" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO125" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP125" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ125" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR125" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS125" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT125" s="1">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -14792,8 +17707,56 @@
         <f t="shared" si="15"/>
         <v>5.1138621680753824E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE126" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF126" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AG126" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AH126" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AI126" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AJ126" s="13">
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="AK126" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AL126" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AM126" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AN126" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AO126" s="13">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="AP126" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AQ126" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR126" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AS126" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AT126" s="13">
+        <v>8.6400000000000005E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -14846,8 +17809,56 @@
         <f t="shared" si="15"/>
         <v>5.834401472729541E-4</v>
       </c>
-    </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE127" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF127" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AG127" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AH127" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AI127" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AJ127" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AK127" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AL127" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AM127" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AN127" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AO127" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AP127" s="1">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AQ127" s="1">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AR127" s="1">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AS127" s="1">
+        <v>8.64</v>
+      </c>
+      <c r="AT127" s="1">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:67" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -14901,7 +17912,7 @@
         <v>7.1160228947361758E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>248</v>
       </c>
@@ -14954,8 +17965,23 @@
         <f t="shared" si="15"/>
         <v>6.7192904177343729E-4</v>
       </c>
-    </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AF129" s="1"/>
+      <c r="AG129" s="1"/>
+      <c r="AH129" s="1"/>
+      <c r="AI129" s="1"/>
+      <c r="AJ129" s="1"/>
+      <c r="AK129" s="1"/>
+      <c r="AL129" s="1"/>
+      <c r="AM129" s="1"/>
+      <c r="AN129" s="1"/>
+      <c r="AO129" s="1"/>
+      <c r="AP129" s="1"/>
+      <c r="AQ129" s="1"/>
+      <c r="AR129" s="1"/>
+      <c r="AS129" s="1"/>
+      <c r="AT129" s="1"/>
+    </row>
+    <row r="130" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>249</v>
       </c>
@@ -15008,8 +18034,23 @@
         <f t="shared" ref="AA130:AA154" si="19">+W130</f>
         <v>6.8402164621609858E-4</v>
       </c>
-    </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AF130" s="1"/>
+      <c r="AG130" s="1"/>
+      <c r="AH130" s="1"/>
+      <c r="AI130" s="1"/>
+      <c r="AJ130" s="1"/>
+      <c r="AK130" s="1"/>
+      <c r="AL130" s="1"/>
+      <c r="AM130" s="1"/>
+      <c r="AN130" s="1"/>
+      <c r="AO130" s="1"/>
+      <c r="AP130" s="1"/>
+      <c r="AQ130" s="1"/>
+      <c r="AR130" s="1"/>
+      <c r="AS130" s="1"/>
+      <c r="AT130" s="1"/>
+    </row>
+    <row r="131" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>250</v>
       </c>
@@ -15062,8 +18103,23 @@
         <f t="shared" si="19"/>
         <v>7.3510433221211555E-4</v>
       </c>
-    </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AF131" s="1"/>
+      <c r="AG131" s="1"/>
+      <c r="AH131" s="1"/>
+      <c r="AI131" s="1"/>
+      <c r="AJ131" s="1"/>
+      <c r="AK131" s="1"/>
+      <c r="AL131" s="1"/>
+      <c r="AM131" s="1"/>
+      <c r="AN131" s="1"/>
+      <c r="AO131" s="1"/>
+      <c r="AP131" s="1"/>
+      <c r="AQ131" s="1"/>
+      <c r="AR131" s="1"/>
+      <c r="AS131" s="1"/>
+      <c r="AT131" s="1"/>
+    </row>
+    <row r="132" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>251</v>
       </c>
@@ -15117,7 +18173,7 @@
         <v>6.8958168854050443E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>252</v>
       </c>
@@ -15171,7 +18227,7 @@
         <v>7.0175093423377206E-4</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>253</v>
       </c>
@@ -15225,7 +18281,7 @@
         <v>9.24392529713391E-4</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>254</v>
       </c>
@@ -15279,7 +18335,7 @@
         <v>4.2679489394130968E-4</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>255</v>
       </c>
@@ -15333,7 +18389,7 @@
         <v>7.0492044974188462E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>256</v>
       </c>
@@ -15387,7 +18443,7 @@
         <v>6.0317831663807579E-4</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>257</v>
       </c>
@@ -15441,7 +18497,7 @@
         <v>5.3431529879549361E-4</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>258</v>
       </c>
@@ -15495,7 +18551,7 @@
         <v>9.2650687165257131E-4</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>259</v>
       </c>
@@ -15549,7 +18605,7 @@
         <v>4.9093461376614072E-4</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>260</v>
       </c>
@@ -15603,7 +18659,7 @@
         <v>4.6471042769603648E-4</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>261</v>
       </c>
@@ -15657,7 +18713,7 @@
         <v>3.9116170433328728E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>262</v>
       </c>
@@ -15711,7 +18767,7 @@
         <v>4.0431038289007962E-4</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:46" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>263</v>
       </c>
@@ -22387,8 +25443,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41008,7 +44065,7 @@
         <v>400</v>
       </c>
       <c r="F2" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -41028,7 +44085,7 @@
         <v>399</v>
       </c>
       <c r="F3" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -41048,7 +44105,7 @@
         <v>401</v>
       </c>
       <c r="F4" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -41068,7 +44125,7 @@
         <v>402</v>
       </c>
       <c r="F5" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -41088,7 +44145,7 @@
         <v>398</v>
       </c>
       <c r="F6" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -41162,7 +44219,7 @@
         <v>400</v>
       </c>
       <c r="F3" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -41182,7 +44239,7 @@
         <v>400</v>
       </c>
       <c r="F4" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -41222,7 +44279,7 @@
         <v>399</v>
       </c>
       <c r="F6" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -41242,7 +44299,7 @@
         <v>399</v>
       </c>
       <c r="F7" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -41282,7 +44339,7 @@
         <v>401</v>
       </c>
       <c r="F9" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -41302,7 +44359,7 @@
         <v>401</v>
       </c>
       <c r="F10" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -41342,7 +44399,7 @@
         <v>402</v>
       </c>
       <c r="F12" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -41362,7 +44419,7 @@
         <v>402</v>
       </c>
       <c r="F13" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -41402,7 +44459,7 @@
         <v>398</v>
       </c>
       <c r="F15" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -41422,7 +44479,7 @@
         <v>398</v>
       </c>
       <c r="F16" s="4">
-        <v>-500</v>
+        <v>-50</v>
       </c>
     </row>
   </sheetData>

--- a/assets/3D/setup.xlsx
+++ b/assets/3D/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\assets\3D\sust yield server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05EA8D0-995C-4015-A8D7-B23A07312039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193EF687-4CBE-4DEC-B582-9A5B7AE67EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="11483" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="1192">
   <si>
     <t>nlay</t>
   </si>
@@ -3570,9 +3570,6 @@
     <t>Run01</t>
   </si>
   <si>
-    <t>Run02</t>
-  </si>
-  <si>
     <t>kv_1E-12_kh_1E-07</t>
   </si>
   <si>
@@ -3618,22 +3615,13 @@
     <t>kv_1E-08_kh_1E-03</t>
   </si>
   <si>
-    <t>kv_1E-06_kh_1E-07</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-06</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-05</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-04</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-03</t>
-  </si>
-  <si>
     <t>Run03</t>
+  </si>
+  <si>
+    <t>Run02.1</t>
+  </si>
+  <si>
+    <t>Run02.2</t>
   </si>
 </sst>
 </file>
@@ -3690,18 +3678,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -3747,7 +3729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3774,9 +3756,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -4423,21 +4402,10 @@
       <c r="H1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1124</v>
-      </c>
+      <c r="I1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
@@ -4464,21 +4432,10 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
+      <c r="I2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
@@ -4491,35 +4448,24 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E3" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F3" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G3" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H3" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I3" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J3" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K3" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M3" s="4">
         <v>-600000</v>
       </c>
+      <c r="I3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
@@ -4532,35 +4478,24 @@
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E4" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F4" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G4" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H4" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I4" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J4" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K4" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M4" s="4">
         <v>-600000</v>
       </c>
+      <c r="I4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
@@ -4587,21 +4522,10 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
@@ -4614,35 +4538,24 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E6" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F6" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G6" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H6" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J6" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K6" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M6" s="4">
         <v>-600000</v>
       </c>
+      <c r="I6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
@@ -4655,35 +4568,24 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E7" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F7" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G7" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H7" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I7" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J7" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K7" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M7" s="4">
         <v>-600000</v>
       </c>
+      <c r="I7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
@@ -4710,21 +4612,10 @@
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
+      <c r="I8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
@@ -4737,35 +4628,24 @@
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E9" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F9" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G9" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H9" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J9" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K9" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M9" s="4">
         <v>-600000</v>
       </c>
+      <c r="I9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
@@ -4778,35 +4658,24 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E10" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F10" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G10" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H10" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I10" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J10" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K10" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M10" s="4">
         <v>-600000</v>
       </c>
+      <c r="I10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
@@ -4833,21 +4702,10 @@
       <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
@@ -4860,35 +4718,24 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E12" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F12" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G12" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H12" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I12" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J12" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K12" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M12" s="4">
         <v>-600000</v>
       </c>
+      <c r="I12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
@@ -4901,35 +4748,24 @@
         <v>0</v>
       </c>
       <c r="D13" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E13" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F13" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G13" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H13" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I13" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J13" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K13" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M13" s="4">
         <v>-600000</v>
       </c>
+      <c r="I13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
@@ -4956,21 +4792,10 @@
       <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
+      <c r="I14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
@@ -4983,35 +4808,24 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E15" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F15" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G15" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H15" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I15" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J15" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K15" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M15" s="4">
         <v>-600000</v>
       </c>
+      <c r="I15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
@@ -5024,35 +4838,24 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>-10</v>
+        <v>-1000</v>
       </c>
       <c r="E16" s="4">
-        <v>-50</v>
+        <v>-10000</v>
       </c>
       <c r="F16" s="4">
-        <v>-100</v>
+        <v>-100000</v>
       </c>
       <c r="G16" s="4">
-        <v>-200</v>
+        <v>-200000</v>
       </c>
       <c r="H16" s="4">
-        <v>-1000</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-2000</v>
-      </c>
-      <c r="J16" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="K16" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M16" s="4">
         <v>-600000</v>
       </c>
+      <c r="I16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
@@ -5297,63 +5100,40 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AO41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="21" width="17.06640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1" s="4" t="s">
         <v>1178</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>1179</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1158</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1159</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>1160</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>1161</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
@@ -5380,55 +5160,29 @@
         <v>50</v>
       </c>
       <c r="B2" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F2" s="1">
         <v>86.4</v>
       </c>
-      <c r="G2" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K2" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L2" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P2" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -5457,53 +5211,27 @@
       <c r="B3" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C3" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="D3" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="E3" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="F3" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G3" s="15">
+      <c r="C3" s="15">
         <v>8.6400000000000006E-8</v>
       </c>
-      <c r="H3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="L3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="M3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="N3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="O3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="P3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -5530,55 +5258,29 @@
         <v>56</v>
       </c>
       <c r="B4" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F4" s="1">
         <v>86.4</v>
       </c>
-      <c r="G4" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L4" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P4" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -5607,53 +5309,27 @@
       <c r="B5" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C5" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="D5" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="E5" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="F5" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="C5" s="15">
         <v>8.6400000000000006E-8</v>
       </c>
-      <c r="H5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="L5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="M5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="N5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="O5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="P5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
@@ -5680,55 +5356,29 @@
         <v>60</v>
       </c>
       <c r="B6" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F6" s="1">
         <v>86.4</v>
       </c>
-      <c r="G6" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K6" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L6" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P6" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -5755,55 +5405,29 @@
         <v>62</v>
       </c>
       <c r="B7" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F7" s="1">
         <v>86.4</v>
       </c>
-      <c r="G7" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K7" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L7" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P7" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -5832,53 +5456,27 @@
       <c r="B8" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C8" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="D8" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="E8" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="F8" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G8" s="15">
+      <c r="C8" s="15">
         <v>8.6400000000000006E-8</v>
       </c>
-      <c r="H8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="L8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="M8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="N8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="O8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="P8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -5905,55 +5503,29 @@
         <v>64</v>
       </c>
       <c r="B9" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F9" s="1">
         <v>86.4</v>
       </c>
-      <c r="G9" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K9" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L9" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P9" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -5982,53 +5554,27 @@
       <c r="B10" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C10" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="D10" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="E10" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="F10" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="C10" s="15">
         <v>8.6400000000000006E-8</v>
       </c>
-      <c r="H10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="L10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="M10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="N10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="O10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="P10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
@@ -6055,55 +5601,29 @@
         <v>66</v>
       </c>
       <c r="B11" s="1">
-        <v>8.6400000000000001E-3</v>
+        <v>86.4</v>
       </c>
       <c r="C11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F11" s="1">
         <v>86.4</v>
       </c>
-      <c r="G11" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="K11" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="L11" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P11" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -6125,6 +5645,481 @@
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
     </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6134,11 +6129,12 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:BO364"/>
+  <dimension ref="A1:BZ364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.46484375" style="4" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
@@ -12052,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>200</v>
       </c>
@@ -12145,7 +12141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>201</v>
       </c>
@@ -12250,7 +12246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>202</v>
       </c>
@@ -12356,7 +12352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>203</v>
       </c>
@@ -12462,7 +12458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>204</v>
       </c>
@@ -12535,7 +12531,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="86" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>205</v>
       </c>
@@ -12608,7 +12604,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="87" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>206</v>
       </c>
@@ -12681,7 +12677,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="88" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>207</v>
       </c>
@@ -12735,7 +12731,7 @@
         <v>6.7755654381398901E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>208</v>
       </c>
@@ -12788,11 +12784,11 @@
         <f t="shared" si="11"/>
         <v>9.4339543613295384E-4</v>
       </c>
-      <c r="BC89" t="s">
+      <c r="BN89" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="90" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -12848,47 +12844,47 @@
       <c r="AE90" t="s">
         <v>1173</v>
       </c>
-      <c r="BC90" s="4" t="s">
+      <c r="BN90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="BD90" s="4" t="s">
+      <c r="BO90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="BE90" s="4" t="s">
+      <c r="BP90" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="BF90" s="4" t="s">
+      <c r="BQ90" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="BG90" s="4" t="s">
+      <c r="BR90" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="BH90" s="4" t="s">
+      <c r="BS90" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="BI90" s="4" t="s">
+      <c r="BT90" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="BJ90" s="4" t="s">
+      <c r="BU90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="BK90" s="4" t="s">
+      <c r="BV90" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="BL90" s="4" t="s">
+      <c r="BW90" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BM90" s="4" t="s">
+      <c r="BX90" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BN90" s="4" t="s">
+      <c r="BY90" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="BO90" s="4" t="s">
+      <c r="BZ90" s="4" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="91" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>210</v>
       </c>
@@ -12945,106 +12941,76 @@
         <v>43</v>
       </c>
       <c r="AF91" s="16" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="AG91" s="16" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="AH91" s="16" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="AI91" s="16" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="AJ91" s="16" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="AK91" s="16" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="AL91" s="16" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="AM91" s="16" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="AN91" s="16" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="AO91" s="16" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AP91" s="19" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AQ91" s="19" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AR91" s="19" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AS91" s="19" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AT91" s="19" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU91" s="19" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AV91" s="19" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AW91" s="19" t="s">
-        <v>1170</v>
-      </c>
-      <c r="AX91" s="19" t="s">
-        <v>1171</v>
-      </c>
-      <c r="AY91" s="19" t="s">
         <v>1172</v>
       </c>
-      <c r="BC91" s="4" t="s">
+      <c r="BN91" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="BD91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN91" s="4">
-        <v>0</v>
       </c>
       <c r="BO91" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>211</v>
       </c>
@@ -13130,77 +13096,47 @@
       <c r="AO92" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP92" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ92" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR92" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS92" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT92" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU92" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV92" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW92" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX92" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY92" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC92" s="4" t="s">
+      <c r="BN92" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD92" s="3">
+      <c r="BO92" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE92" s="4">
+      <c r="BP92" s="4">
         <v>0</v>
       </c>
-      <c r="BF92" s="4">
+      <c r="BQ92" s="4">
         <v>-100</v>
       </c>
-      <c r="BG92" s="4">
+      <c r="BR92" s="4">
         <v>-200</v>
       </c>
-      <c r="BH92" s="4">
+      <c r="BS92" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI92" s="4">
+      <c r="BT92" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ92" s="4">
+      <c r="BU92" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK92" s="4">
+      <c r="BV92" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL92" s="4">
+      <c r="BW92" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM92" s="4">
+      <c r="BX92" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN92" s="4">
+      <c r="BY92" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO92" s="4">
+      <c r="BZ92" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="93" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>212</v>
       </c>
@@ -13257,106 +13193,76 @@
         <v>54</v>
       </c>
       <c r="AF93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO93" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU93" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="BC93" s="4" t="s">
+      <c r="BN93" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD93" s="3">
+      <c r="BO93" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE93" s="4">
+      <c r="BP93" s="4">
         <v>0</v>
       </c>
-      <c r="BF93" s="4">
+      <c r="BQ93" s="4">
         <v>-100</v>
       </c>
-      <c r="BG93" s="4">
+      <c r="BR93" s="4">
         <v>-200</v>
       </c>
-      <c r="BH93" s="4">
+      <c r="BS93" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI93" s="4">
+      <c r="BT93" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ93" s="4">
+      <c r="BU93" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK93" s="4">
+      <c r="BV93" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL93" s="4">
+      <c r="BW93" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM93" s="4">
+      <c r="BX93" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN93" s="4">
+      <c r="BY93" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO93" s="4">
+      <c r="BZ93" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="94" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>213</v>
       </c>
@@ -13442,77 +13348,47 @@
       <c r="AO94" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP94" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ94" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR94" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS94" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT94" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU94" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV94" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW94" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX94" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY94" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC94" s="4" t="s">
+      <c r="BN94" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="BD94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN94" s="4">
-        <v>0</v>
       </c>
       <c r="BO94" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>214</v>
       </c>
@@ -13569,106 +13445,76 @@
         <v>58</v>
       </c>
       <c r="AF95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO95" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU95" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="BC95" s="4" t="s">
+      <c r="BN95" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD95" s="3">
+      <c r="BO95" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE95" s="4">
+      <c r="BP95" s="4">
         <v>0</v>
       </c>
-      <c r="BF95" s="4">
+      <c r="BQ95" s="4">
         <v>-100</v>
       </c>
-      <c r="BG95" s="4">
+      <c r="BR95" s="4">
         <v>-200</v>
       </c>
-      <c r="BH95" s="4">
+      <c r="BS95" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI95" s="4">
+      <c r="BT95" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ95" s="4">
+      <c r="BU95" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK95" s="4">
+      <c r="BV95" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL95" s="4">
+      <c r="BW95" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM95" s="4">
+      <c r="BX95" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN95" s="4">
+      <c r="BY95" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO95" s="4">
+      <c r="BZ95" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="96" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>215</v>
       </c>
@@ -13754,77 +13600,47 @@
       <c r="AO96" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP96" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ96" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR96" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS96" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT96" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU96" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV96" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW96" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX96" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY96" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC96" s="4" t="s">
+      <c r="BN96" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD96" s="3">
+      <c r="BO96" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE96" s="4">
+      <c r="BP96" s="4">
         <v>0</v>
       </c>
-      <c r="BF96" s="4">
+      <c r="BQ96" s="4">
         <v>-100</v>
       </c>
-      <c r="BG96" s="4">
+      <c r="BR96" s="4">
         <v>-200</v>
       </c>
-      <c r="BH96" s="4">
+      <c r="BS96" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI96" s="4">
+      <c r="BT96" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ96" s="4">
+      <c r="BU96" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK96" s="4">
+      <c r="BV96" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL96" s="4">
+      <c r="BW96" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM96" s="4">
+      <c r="BX96" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN96" s="4">
+      <c r="BY96" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO96" s="4">
+      <c r="BZ96" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="97" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -13910,77 +13726,47 @@
       <c r="AO97" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP97" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ97" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR97" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS97" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT97" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU97" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV97" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW97" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX97" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY97" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC97" s="4" t="s">
+      <c r="BN97" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="BD97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN97" s="4">
-        <v>0</v>
       </c>
       <c r="BO97" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>217</v>
       </c>
@@ -14037,106 +13823,76 @@
         <v>63</v>
       </c>
       <c r="AF98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO98" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU98" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="BC98" s="4" t="s">
+      <c r="BN98" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD98" s="3">
+      <c r="BO98" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE98" s="4">
+      <c r="BP98" s="4">
         <v>0</v>
       </c>
-      <c r="BF98" s="4">
+      <c r="BQ98" s="4">
         <v>-100</v>
       </c>
-      <c r="BG98" s="4">
+      <c r="BR98" s="4">
         <v>-200</v>
       </c>
-      <c r="BH98" s="4">
+      <c r="BS98" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI98" s="4">
+      <c r="BT98" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ98" s="4">
+      <c r="BU98" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK98" s="4">
+      <c r="BV98" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL98" s="4">
+      <c r="BW98" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM98" s="4">
+      <c r="BX98" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN98" s="4">
+      <c r="BY98" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO98" s="4">
+      <c r="BZ98" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="99" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>218</v>
       </c>
@@ -14222,77 +13978,47 @@
       <c r="AO99" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP99" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ99" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR99" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS99" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT99" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU99" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV99" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW99" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX99" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY99" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC99" s="4" t="s">
+      <c r="BN99" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD99" s="3">
+      <c r="BO99" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE99" s="4">
+      <c r="BP99" s="4">
         <v>0</v>
       </c>
-      <c r="BF99" s="4">
+      <c r="BQ99" s="4">
         <v>-100</v>
       </c>
-      <c r="BG99" s="4">
+      <c r="BR99" s="4">
         <v>-200</v>
       </c>
-      <c r="BH99" s="4">
+      <c r="BS99" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI99" s="4">
+      <c r="BT99" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ99" s="4">
+      <c r="BU99" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK99" s="4">
+      <c r="BV99" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL99" s="4">
+      <c r="BW99" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM99" s="4">
+      <c r="BX99" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN99" s="4">
+      <c r="BY99" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO99" s="4">
+      <c r="BZ99" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="100" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>219</v>
       </c>
@@ -14349,106 +14075,76 @@
         <v>65</v>
       </c>
       <c r="AF100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO100" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU100" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="BC100" s="4" t="s">
+      <c r="BN100" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="BD100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN100" s="4">
-        <v>0</v>
       </c>
       <c r="BO100" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>220</v>
       </c>
@@ -14534,77 +14230,47 @@
       <c r="AO101" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP101" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ101" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR101" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS101" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT101" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU101" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV101" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW101" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX101" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY101" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="BC101" s="4" t="s">
+      <c r="BN101" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD101" s="3">
+      <c r="BO101" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE101" s="4">
+      <c r="BP101" s="4">
         <v>0</v>
       </c>
-      <c r="BF101" s="4">
+      <c r="BQ101" s="4">
         <v>-100</v>
       </c>
-      <c r="BG101" s="4">
+      <c r="BR101" s="4">
         <v>-200</v>
       </c>
-      <c r="BH101" s="4">
+      <c r="BS101" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI101" s="4">
+      <c r="BT101" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ101" s="4">
+      <c r="BU101" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK101" s="4">
+      <c r="BV101" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL101" s="4">
+      <c r="BW101" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM101" s="4">
+      <c r="BX101" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN101" s="4">
+      <c r="BY101" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO101" s="4">
+      <c r="BZ101" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="102" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -14657,47 +14323,47 @@
         <f t="shared" si="15"/>
         <v>4.7180228576033662E-4</v>
       </c>
-      <c r="BC102" s="4" t="s">
+      <c r="BN102" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD102" s="3">
+      <c r="BO102" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE102" s="4">
+      <c r="BP102" s="4">
         <v>0</v>
       </c>
-      <c r="BF102" s="4">
+      <c r="BQ102" s="4">
         <v>-100</v>
       </c>
-      <c r="BG102" s="4">
+      <c r="BR102" s="4">
         <v>-200</v>
       </c>
-      <c r="BH102" s="4">
+      <c r="BS102" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI102" s="4">
+      <c r="BT102" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ102" s="4">
+      <c r="BU102" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK102" s="4">
+      <c r="BV102" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL102" s="4">
+      <c r="BW102" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM102" s="4">
+      <c r="BX102" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN102" s="4">
+      <c r="BY102" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO102" s="4">
+      <c r="BZ102" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="103" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>222</v>
       </c>
@@ -14751,49 +14417,49 @@
         <v>6.1373542849109256E-4</v>
       </c>
       <c r="AE103" s="14" t="s">
-        <v>1174</v>
-      </c>
-      <c r="BC103" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="BN103" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="BD103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN103" s="4">
-        <v>0</v>
       </c>
       <c r="BO103" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>223</v>
       </c>
@@ -14865,19 +14531,19 @@
         <v>1157</v>
       </c>
       <c r="AK104" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AL104" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="AL104" s="4" t="s">
+      <c r="AM104" s="4" t="s">
         <v>1176</v>
       </c>
-      <c r="AM104" s="4" t="s">
+      <c r="AN104" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="AN104" s="4" t="s">
+      <c r="AO104" s="4" t="s">
         <v>1178</v>
-      </c>
-      <c r="AO104" s="4" t="s">
-        <v>1179</v>
       </c>
       <c r="AP104" s="4" t="s">
         <v>1158</v>
@@ -14894,47 +14560,47 @@
       <c r="AT104" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="BC104" s="4" t="s">
+      <c r="BN104" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD104" s="3">
+      <c r="BO104" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE104" s="4">
+      <c r="BP104" s="4">
         <v>0</v>
       </c>
-      <c r="BF104" s="4">
+      <c r="BQ104" s="4">
         <v>-100</v>
       </c>
-      <c r="BG104" s="4">
+      <c r="BR104" s="4">
         <v>-200</v>
       </c>
-      <c r="BH104" s="4">
+      <c r="BS104" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI104" s="4">
+      <c r="BT104" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ104" s="4">
+      <c r="BU104" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK104" s="4">
+      <c r="BV104" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL104" s="4">
+      <c r="BW104" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM104" s="4">
+      <c r="BX104" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN104" s="4">
+      <c r="BY104" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO104" s="4">
+      <c r="BZ104" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="105" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -15035,47 +14701,47 @@
       <c r="AT105" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC105" s="4" t="s">
+      <c r="BN105" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD105" s="3">
+      <c r="BO105" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE105" s="4">
+      <c r="BP105" s="4">
         <v>0</v>
       </c>
-      <c r="BF105" s="4">
+      <c r="BQ105" s="4">
         <v>-100</v>
       </c>
-      <c r="BG105" s="4">
+      <c r="BR105" s="4">
         <v>-200</v>
       </c>
-      <c r="BH105" s="4">
+      <c r="BS105" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI105" s="4">
+      <c r="BT105" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ105" s="4">
+      <c r="BU105" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK105" s="4">
+      <c r="BV105" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL105" s="4">
+      <c r="BW105" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM105" s="4">
+      <c r="BX105" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN105" s="4">
+      <c r="BY105" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO105" s="4">
+      <c r="BZ105" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="106" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -15177,7 +14843,7 @@
         <v>8.6400000000000001E-7</v>
       </c>
     </row>
-    <row r="107" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -15279,7 +14945,7 @@
         <v>86.4</v>
       </c>
     </row>
-    <row r="108" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>227</v>
       </c>
@@ -15380,11 +15046,11 @@
       <c r="AT108" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC108" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="109" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BN108" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="109" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>228</v>
       </c>
@@ -15485,47 +15151,47 @@
       <c r="AT109" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC109" s="4" t="s">
+      <c r="BN109" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="BD109" s="4" t="s">
+      <c r="BO109" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="BE109" s="4" t="s">
+      <c r="BP109" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="BF109" s="4" t="s">
+      <c r="BQ109" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="BG109" s="4" t="s">
+      <c r="BR109" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="BH109" s="4" t="s">
+      <c r="BS109" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="BI109" s="4" t="s">
+      <c r="BT109" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="BJ109" s="4" t="s">
+      <c r="BU109" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="BK109" s="4" t="s">
+      <c r="BV109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="BL109" s="4" t="s">
+      <c r="BW109" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BM109" s="4" t="s">
+      <c r="BX109" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BN109" s="4" t="s">
+      <c r="BY109" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="BO109" s="4" t="s">
+      <c r="BZ109" s="4" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="110" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>229</v>
       </c>
@@ -15626,47 +15292,47 @@
       <c r="AT110" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC110" s="4" t="s">
+      <c r="BN110" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="BD110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN110" s="4">
-        <v>0</v>
       </c>
       <c r="BO110" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>230</v>
       </c>
@@ -15767,47 +15433,47 @@
       <c r="AT111" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC111" s="4" t="s">
+      <c r="BN111" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD111" s="3">
+      <c r="BO111" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE111" s="4">
+      <c r="BP111" s="4">
         <v>0</v>
       </c>
-      <c r="BF111" s="4">
+      <c r="BQ111" s="4">
         <v>-10</v>
       </c>
-      <c r="BG111" s="4">
+      <c r="BR111" s="4">
         <v>-50</v>
       </c>
-      <c r="BH111" s="4">
+      <c r="BS111" s="4">
         <v>-100</v>
       </c>
-      <c r="BI111" s="4">
+      <c r="BT111" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ111" s="4">
+      <c r="BU111" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK111" s="4">
+      <c r="BV111" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL111" s="4">
+      <c r="BW111" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM111" s="4">
+      <c r="BX111" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN111" s="4">
+      <c r="BY111" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO111" s="4">
+      <c r="BZ111" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="112" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>231</v>
       </c>
@@ -15908,47 +15574,47 @@
       <c r="AT112" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC112" s="4" t="s">
+      <c r="BN112" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD112" s="3">
+      <c r="BO112" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE112" s="4">
+      <c r="BP112" s="4">
         <v>0</v>
       </c>
-      <c r="BF112" s="4">
+      <c r="BQ112" s="4">
         <v>-10</v>
       </c>
-      <c r="BG112" s="4">
+      <c r="BR112" s="4">
         <v>-50</v>
       </c>
-      <c r="BH112" s="4">
+      <c r="BS112" s="4">
         <v>-100</v>
       </c>
-      <c r="BI112" s="4">
+      <c r="BT112" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ112" s="4">
+      <c r="BU112" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK112" s="4">
+      <c r="BV112" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL112" s="4">
+      <c r="BW112" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM112" s="4">
+      <c r="BX112" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN112" s="4">
+      <c r="BY112" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO112" s="4">
+      <c r="BZ112" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="113" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>232</v>
       </c>
@@ -16049,47 +15715,47 @@
       <c r="AT113" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC113" s="4" t="s">
+      <c r="BN113" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="BD113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN113" s="4">
-        <v>0</v>
       </c>
       <c r="BO113" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -16190,47 +15856,47 @@
       <c r="AT114" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC114" s="4" t="s">
+      <c r="BN114" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD114" s="3">
+      <c r="BO114" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE114" s="4">
+      <c r="BP114" s="4">
         <v>0</v>
       </c>
-      <c r="BF114" s="4">
+      <c r="BQ114" s="4">
         <v>-10</v>
       </c>
-      <c r="BG114" s="4">
+      <c r="BR114" s="4">
         <v>-50</v>
       </c>
-      <c r="BH114" s="4">
+      <c r="BS114" s="4">
         <v>-100</v>
       </c>
-      <c r="BI114" s="4">
+      <c r="BT114" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ114" s="4">
+      <c r="BU114" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK114" s="4">
+      <c r="BV114" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL114" s="4">
+      <c r="BW114" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM114" s="4">
+      <c r="BX114" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN114" s="4">
+      <c r="BY114" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO114" s="4">
+      <c r="BZ114" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="115" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -16283,47 +15949,47 @@
         <f t="shared" si="15"/>
         <v>5.5438130895789643E-4</v>
       </c>
-      <c r="BC115" s="4" t="s">
+      <c r="BN115" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD115" s="3">
+      <c r="BO115" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE115" s="4">
+      <c r="BP115" s="4">
         <v>0</v>
       </c>
-      <c r="BF115" s="4">
+      <c r="BQ115" s="4">
         <v>-10</v>
       </c>
-      <c r="BG115" s="4">
+      <c r="BR115" s="4">
         <v>-50</v>
       </c>
-      <c r="BH115" s="4">
+      <c r="BS115" s="4">
         <v>-100</v>
       </c>
-      <c r="BI115" s="4">
+      <c r="BT115" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ115" s="4">
+      <c r="BU115" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK115" s="4">
+      <c r="BV115" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL115" s="4">
+      <c r="BW115" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM115" s="4">
+      <c r="BX115" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN115" s="4">
+      <c r="BY115" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO115" s="4">
+      <c r="BZ115" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="116" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>235</v>
       </c>
@@ -16377,54 +16043,54 @@
         <v>9.0184342071178349E-4</v>
       </c>
       <c r="AE116" s="14" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
       <c r="AH116" s="4"/>
       <c r="AI116" s="4"/>
       <c r="AJ116" s="4"/>
-      <c r="BC116" s="4" t="s">
+      <c r="BN116" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="BD116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN116" s="4">
-        <v>0</v>
       </c>
       <c r="BO116" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ116" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>236</v>
       </c>
@@ -16481,91 +16147,111 @@
         <v>43</v>
       </c>
       <c r="AF117" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="AG117" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="AG117" s="4" t="s">
+      <c r="AH117" s="4" t="s">
         <v>1181</v>
       </c>
-      <c r="AH117" s="4" t="s">
+      <c r="AI117" s="4" t="s">
         <v>1182</v>
       </c>
-      <c r="AI117" s="4" t="s">
+      <c r="AJ117" s="4" t="s">
         <v>1183</v>
       </c>
-      <c r="AJ117" s="4" t="s">
+      <c r="AK117" s="16" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AL117" s="16" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AM117" s="16" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AN117" s="16" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AO117" s="16" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AP117" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="AK117" s="4" t="s">
+      <c r="AQ117" s="4" t="s">
         <v>1185</v>
       </c>
-      <c r="AL117" s="4" t="s">
+      <c r="AR117" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="AM117" s="4" t="s">
+      <c r="AS117" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="AN117" s="4" t="s">
+      <c r="AT117" s="4" t="s">
         <v>1188</v>
       </c>
-      <c r="AO117" s="4" t="s">
-        <v>1189</v>
-      </c>
-      <c r="AP117" s="4" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AQ117" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="AR117" s="4" t="s">
-        <v>1192</v>
-      </c>
-      <c r="AS117" s="4" t="s">
-        <v>1193</v>
-      </c>
-      <c r="AT117" s="4" t="s">
-        <v>1194</v>
-      </c>
-      <c r="BC117" s="4" t="s">
+      <c r="AU117" s="16" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AV117" s="16" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AW117" s="16" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AX117" s="16" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AY117" s="16" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AZ117" s="4"/>
+      <c r="BA117" s="4"/>
+      <c r="BB117" s="4"/>
+      <c r="BC117" s="4"/>
+      <c r="BD117" s="4"/>
+      <c r="BN117" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD117" s="3">
+      <c r="BO117" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE117" s="4">
+      <c r="BP117" s="4">
         <v>0</v>
       </c>
-      <c r="BF117" s="4">
+      <c r="BQ117" s="4">
         <v>-10</v>
       </c>
-      <c r="BG117" s="4">
+      <c r="BR117" s="4">
         <v>-50</v>
       </c>
-      <c r="BH117" s="4">
+      <c r="BS117" s="4">
         <v>-100</v>
       </c>
-      <c r="BI117" s="4">
+      <c r="BT117" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ117" s="4">
+      <c r="BU117" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK117" s="4">
+      <c r="BV117" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL117" s="4">
+      <c r="BW117" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM117" s="4">
+      <c r="BX117" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN117" s="4">
+      <c r="BY117" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO117" s="4">
+      <c r="BZ117" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="118" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>237</v>
       </c>
@@ -16636,19 +16322,19 @@
       <c r="AJ118" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK118" s="1">
+      <c r="AK118" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL118" s="1">
+      <c r="AL118" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM118" s="1">
+      <c r="AM118" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN118" s="1">
+      <c r="AN118" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO118" s="1">
+      <c r="AO118" s="17">
         <v>86.4</v>
       </c>
       <c r="AP118" s="1">
@@ -16666,47 +16352,67 @@
       <c r="AT118" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC118" s="4" t="s">
+      <c r="AU118" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV118" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW118" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX118" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY118" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ118" s="1"/>
+      <c r="BA118" s="1"/>
+      <c r="BB118" s="1"/>
+      <c r="BC118" s="1"/>
+      <c r="BD118" s="1"/>
+      <c r="BN118" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD118" s="3">
+      <c r="BO118" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE118" s="4">
+      <c r="BP118" s="4">
         <v>0</v>
       </c>
-      <c r="BF118" s="4">
+      <c r="BQ118" s="4">
         <v>-10</v>
       </c>
-      <c r="BG118" s="4">
+      <c r="BR118" s="4">
         <v>-50</v>
       </c>
-      <c r="BH118" s="4">
+      <c r="BS118" s="4">
         <v>-100</v>
       </c>
-      <c r="BI118" s="4">
+      <c r="BT118" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ118" s="4">
+      <c r="BU118" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK118" s="4">
+      <c r="BV118" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL118" s="4">
+      <c r="BW118" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM118" s="4">
+      <c r="BX118" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN118" s="4">
+      <c r="BY118" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO118" s="4">
+      <c r="BZ118" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="119" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -16777,77 +16483,97 @@
       <c r="AJ119" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK119" s="13">
+      <c r="AK119" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL119" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM119" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN119" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO119" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL119" s="13">
+      <c r="AQ119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM119" s="13">
+      <c r="AR119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN119" s="13">
+      <c r="AS119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO119" s="13">
+      <c r="AT119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC119" s="4" t="s">
+      <c r="AU119" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV119" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW119" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX119" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY119" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ119" s="13"/>
+      <c r="BA119" s="13"/>
+      <c r="BB119" s="13"/>
+      <c r="BC119" s="13"/>
+      <c r="BD119" s="13"/>
+      <c r="BN119" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="BD119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN119" s="4">
-        <v>0</v>
       </c>
       <c r="BO119" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -16918,19 +16644,19 @@
       <c r="AJ120" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK120" s="1">
+      <c r="AK120" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL120" s="1">
+      <c r="AL120" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM120" s="1">
+      <c r="AM120" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN120" s="1">
+      <c r="AN120" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO120" s="1">
+      <c r="AO120" s="17">
         <v>86.4</v>
       </c>
       <c r="AP120" s="1">
@@ -16948,47 +16674,67 @@
       <c r="AT120" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC120" s="4" t="s">
+      <c r="AU120" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV120" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW120" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX120" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY120" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ120" s="1"/>
+      <c r="BA120" s="1"/>
+      <c r="BB120" s="1"/>
+      <c r="BC120" s="1"/>
+      <c r="BD120" s="1"/>
+      <c r="BN120" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD120" s="3">
+      <c r="BO120" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE120" s="4">
+      <c r="BP120" s="4">
         <v>0</v>
       </c>
-      <c r="BF120" s="4">
+      <c r="BQ120" s="4">
         <v>-10</v>
       </c>
-      <c r="BG120" s="4">
+      <c r="BR120" s="4">
         <v>-50</v>
       </c>
-      <c r="BH120" s="4">
+      <c r="BS120" s="4">
         <v>-100</v>
       </c>
-      <c r="BI120" s="4">
+      <c r="BT120" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ120" s="4">
+      <c r="BU120" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK120" s="4">
+      <c r="BV120" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL120" s="4">
+      <c r="BW120" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM120" s="4">
+      <c r="BX120" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN120" s="4">
+      <c r="BY120" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO120" s="4">
+      <c r="BZ120" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="121" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -17059,77 +16805,97 @@
       <c r="AJ121" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK121" s="13">
+      <c r="AK121" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL121" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM121" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN121" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO121" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL121" s="13">
+      <c r="AQ121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM121" s="13">
+      <c r="AR121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN121" s="13">
+      <c r="AS121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO121" s="13">
+      <c r="AT121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC121" s="4" t="s">
+      <c r="AU121" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV121" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW121" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX121" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY121" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ121" s="13"/>
+      <c r="BA121" s="13"/>
+      <c r="BB121" s="13"/>
+      <c r="BC121" s="13"/>
+      <c r="BD121" s="13"/>
+      <c r="BN121" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD121" s="3">
+      <c r="BO121" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE121" s="4">
+      <c r="BP121" s="4">
         <v>0</v>
       </c>
-      <c r="BF121" s="4">
+      <c r="BQ121" s="4">
         <v>-10</v>
       </c>
-      <c r="BG121" s="4">
+      <c r="BR121" s="4">
         <v>-50</v>
       </c>
-      <c r="BH121" s="4">
+      <c r="BS121" s="4">
         <v>-100</v>
       </c>
-      <c r="BI121" s="4">
+      <c r="BT121" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ121" s="4">
+      <c r="BU121" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK121" s="4">
+      <c r="BV121" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL121" s="4">
+      <c r="BW121" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM121" s="4">
+      <c r="BX121" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN121" s="4">
+      <c r="BY121" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO121" s="4">
+      <c r="BZ121" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="122" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>241</v>
       </c>
@@ -17200,19 +16966,19 @@
       <c r="AJ122" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK122" s="1">
+      <c r="AK122" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL122" s="1">
+      <c r="AL122" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM122" s="1">
+      <c r="AM122" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN122" s="1">
+      <c r="AN122" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO122" s="1">
+      <c r="AO122" s="17">
         <v>86.4</v>
       </c>
       <c r="AP122" s="1">
@@ -17230,47 +16996,67 @@
       <c r="AT122" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC122" s="4" t="s">
+      <c r="AU122" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV122" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW122" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX122" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY122" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ122" s="1"/>
+      <c r="BA122" s="1"/>
+      <c r="BB122" s="1"/>
+      <c r="BC122" s="1"/>
+      <c r="BD122" s="1"/>
+      <c r="BN122" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="BD122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN122" s="4">
-        <v>0</v>
       </c>
       <c r="BO122" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>242</v>
       </c>
@@ -17341,19 +17127,19 @@
       <c r="AJ123" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK123" s="1">
+      <c r="AK123" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL123" s="1">
+      <c r="AL123" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM123" s="1">
+      <c r="AM123" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN123" s="1">
+      <c r="AN123" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO123" s="1">
+      <c r="AO123" s="17">
         <v>86.4</v>
       </c>
       <c r="AP123" s="1">
@@ -17371,47 +17157,67 @@
       <c r="AT123" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC123" s="4" t="s">
+      <c r="AU123" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV123" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW123" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX123" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY123" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ123" s="1"/>
+      <c r="BA123" s="1"/>
+      <c r="BB123" s="1"/>
+      <c r="BC123" s="1"/>
+      <c r="BD123" s="1"/>
+      <c r="BN123" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD123" s="3">
+      <c r="BO123" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE123" s="4">
+      <c r="BP123" s="4">
         <v>0</v>
       </c>
-      <c r="BF123" s="4">
+      <c r="BQ123" s="4">
         <v>-10</v>
       </c>
-      <c r="BG123" s="4">
+      <c r="BR123" s="4">
         <v>-50</v>
       </c>
-      <c r="BH123" s="4">
+      <c r="BS123" s="4">
         <v>-100</v>
       </c>
-      <c r="BI123" s="4">
+      <c r="BT123" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ123" s="4">
+      <c r="BU123" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK123" s="4">
+      <c r="BV123" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL123" s="4">
+      <c r="BW123" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM123" s="4">
+      <c r="BX123" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN123" s="4">
+      <c r="BY123" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO123" s="4">
+      <c r="BZ123" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="124" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>243</v>
       </c>
@@ -17482,77 +17288,97 @@
       <c r="AJ124" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK124" s="13">
+      <c r="AK124" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL124" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM124" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN124" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO124" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL124" s="13">
+      <c r="AQ124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM124" s="13">
+      <c r="AR124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN124" s="13">
+      <c r="AS124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO124" s="13">
+      <c r="AT124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC124" s="4" t="s">
+      <c r="AU124" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV124" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW124" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX124" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY124" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ124" s="13"/>
+      <c r="BA124" s="13"/>
+      <c r="BB124" s="13"/>
+      <c r="BC124" s="13"/>
+      <c r="BD124" s="13"/>
+      <c r="BN124" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD124" s="3">
+      <c r="BO124" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE124" s="4">
+      <c r="BP124" s="4">
         <v>0</v>
       </c>
-      <c r="BF124" s="4">
+      <c r="BQ124" s="4">
         <v>-10</v>
       </c>
-      <c r="BG124" s="4">
+      <c r="BR124" s="4">
         <v>-50</v>
       </c>
-      <c r="BH124" s="4">
+      <c r="BS124" s="4">
         <v>-100</v>
       </c>
-      <c r="BI124" s="4">
+      <c r="BT124" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ124" s="4">
+      <c r="BU124" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK124" s="4">
+      <c r="BV124" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL124" s="4">
+      <c r="BW124" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM124" s="4">
+      <c r="BX124" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN124" s="4">
+      <c r="BY124" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO124" s="4">
+      <c r="BZ124" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="125" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -17623,19 +17449,19 @@
       <c r="AJ125" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK125" s="1">
+      <c r="AK125" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL125" s="1">
+      <c r="AL125" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM125" s="1">
+      <c r="AM125" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN125" s="1">
+      <c r="AN125" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO125" s="1">
+      <c r="AO125" s="17">
         <v>86.4</v>
       </c>
       <c r="AP125" s="1">
@@ -17653,8 +17479,28 @@
       <c r="AT125" s="1">
         <v>86.4</v>
       </c>
-    </row>
-    <row r="126" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU125" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV125" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW125" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX125" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY125" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ125" s="1"/>
+      <c r="BA125" s="1"/>
+      <c r="BB125" s="1"/>
+      <c r="BC125" s="1"/>
+      <c r="BD125" s="1"/>
+    </row>
+    <row r="126" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -17725,38 +17571,58 @@
       <c r="AJ126" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK126" s="13">
+      <c r="AK126" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL126" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM126" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN126" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO126" s="18">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL126" s="13">
+      <c r="AQ126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM126" s="13">
+      <c r="AR126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN126" s="13">
+      <c r="AS126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO126" s="13">
+      <c r="AT126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU126" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV126" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW126" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX126" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY126" s="18">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ126" s="13"/>
+      <c r="BA126" s="13"/>
+      <c r="BB126" s="13"/>
+      <c r="BC126" s="13"/>
+      <c r="BD126" s="13"/>
+    </row>
+    <row r="127" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -17827,19 +17693,19 @@
       <c r="AJ127" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK127" s="1">
+      <c r="AK127" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL127" s="1">
+      <c r="AL127" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM127" s="1">
+      <c r="AM127" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN127" s="1">
+      <c r="AN127" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO127" s="1">
+      <c r="AO127" s="17">
         <v>86.4</v>
       </c>
       <c r="AP127" s="1">
@@ -17857,8 +17723,31 @@
       <c r="AT127" s="1">
         <v>86.4</v>
       </c>
-    </row>
-    <row r="128" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU127" s="17">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV127" s="17">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW127" s="17">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX127" s="17">
+        <v>8.64</v>
+      </c>
+      <c r="AY127" s="17">
+        <v>86.4</v>
+      </c>
+      <c r="AZ127" s="1"/>
+      <c r="BA127" s="1"/>
+      <c r="BB127" s="1"/>
+      <c r="BC127" s="1"/>
+      <c r="BD127" s="1"/>
+      <c r="BN127" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="128" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -17911,8 +17800,43 @@
         <f t="shared" si="15"/>
         <v>7.1160228947361758E-4</v>
       </c>
-    </row>
-    <row r="129" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN128" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO128" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BP128" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ128" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BR128" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BS128" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BT128" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU128" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BV128" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BW128" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BX128" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BY128" s="4"/>
+      <c r="BZ128" s="4"/>
+    </row>
+    <row r="129" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>248</v>
       </c>
@@ -17964,6 +17888,9 @@
       <c r="AA129" s="1">
         <f t="shared" si="15"/>
         <v>6.7192904177343729E-4</v>
+      </c>
+      <c r="AE129" s="14" t="s">
+        <v>1189</v>
       </c>
       <c r="AF129" s="1"/>
       <c r="AG129" s="1"/>
@@ -17980,8 +17907,41 @@
       <c r="AR129" s="1"/>
       <c r="AS129" s="1"/>
       <c r="AT129" s="1"/>
-    </row>
-    <row r="130" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN129" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>249</v>
       </c>
@@ -18034,8 +17994,15 @@
         <f t="shared" ref="AA130:AA154" si="19">+W130</f>
         <v>6.8402164621609858E-4</v>
       </c>
-      <c r="AF130" s="1"/>
-      <c r="AG130" s="1"/>
+      <c r="AE130" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF130" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AG130" s="4" t="s">
+        <v>1178</v>
+      </c>
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
@@ -18049,8 +18016,41 @@
       <c r="AR130" s="1"/>
       <c r="AS130" s="1"/>
       <c r="AT130" s="1"/>
-    </row>
-    <row r="131" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN130" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO130" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP130" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ130" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR130" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS130" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT130" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU130" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV130" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW130" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX130" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>250</v>
       </c>
@@ -18103,8 +18103,15 @@
         <f t="shared" si="19"/>
         <v>7.3510433221211555E-4</v>
       </c>
-      <c r="AF131" s="1"/>
-      <c r="AG131" s="1"/>
+      <c r="AE131" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF131" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG131" s="1">
+        <v>86.4</v>
+      </c>
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
@@ -18118,8 +18125,41 @@
       <c r="AR131" s="1"/>
       <c r="AS131" s="1"/>
       <c r="AT131" s="1"/>
-    </row>
-    <row r="132" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN131" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO131" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP131" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ131" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR131" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS131" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT131" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU131" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV131" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW131" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX131" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>251</v>
       </c>
@@ -18172,8 +18212,50 @@
         <f t="shared" si="19"/>
         <v>6.8958168854050443E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE132" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF132" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG132" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="BN132" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>252</v>
       </c>
@@ -18226,8 +18308,50 @@
         <f t="shared" si="19"/>
         <v>7.0175093423377206E-4</v>
       </c>
-    </row>
-    <row r="134" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE133" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF133" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG133" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BN133" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO133" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ133" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR133" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS133" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT133" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU133" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV133" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW133" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX133" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>253</v>
       </c>
@@ -18280,8 +18404,50 @@
         <f t="shared" si="19"/>
         <v>9.24392529713391E-4</v>
       </c>
-    </row>
-    <row r="135" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE134" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF134" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG134" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="BN134" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO134" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ134" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR134" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS134" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT134" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU134" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV134" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW134" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX134" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>254</v>
       </c>
@@ -18334,8 +18500,50 @@
         <f t="shared" si="19"/>
         <v>4.2679489394130968E-4</v>
       </c>
-    </row>
-    <row r="136" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE135" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF135" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG135" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BN135" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>255</v>
       </c>
@@ -18388,8 +18596,50 @@
         <f t="shared" si="19"/>
         <v>7.0492044974188462E-4</v>
       </c>
-    </row>
-    <row r="137" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE136" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF136" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG136" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BN136" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO136" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ136" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR136" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS136" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT136" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU136" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV136" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW136" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX136" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>256</v>
       </c>
@@ -18442,8 +18692,50 @@
         <f t="shared" si="19"/>
         <v>6.0317831663807579E-4</v>
       </c>
-    </row>
-    <row r="138" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE137" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF137" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG137" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="BN137" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO137" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ137" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR137" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS137" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT137" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU137" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV137" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW137" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX137" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>257</v>
       </c>
@@ -18496,8 +18788,50 @@
         <f t="shared" si="19"/>
         <v>5.3431529879549361E-4</v>
       </c>
-    </row>
-    <row r="139" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE138" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF138" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG138" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BN138" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX138" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>258</v>
       </c>
@@ -18550,8 +18884,50 @@
         <f t="shared" si="19"/>
         <v>9.2650687165257131E-4</v>
       </c>
-    </row>
-    <row r="140" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE139" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF139" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG139" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
+      <c r="BN139" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO139" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP139" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ139" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR139" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS139" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT139" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU139" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV139" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW139" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX139" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>259</v>
       </c>
@@ -18604,8 +18980,50 @@
         <f t="shared" si="19"/>
         <v>4.9093461376614072E-4</v>
       </c>
-    </row>
-    <row r="141" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="AE140" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF140" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG140" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="BN140" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO140" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP140" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ140" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR140" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS140" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT140" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU140" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV140" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW140" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX140" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>260</v>
       </c>
@@ -18658,8 +19076,41 @@
         <f t="shared" si="19"/>
         <v>4.6471042769603648E-4</v>
       </c>
-    </row>
-    <row r="142" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN141" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX141" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>261</v>
       </c>
@@ -18712,8 +19163,41 @@
         <f t="shared" si="19"/>
         <v>3.9116170433328728E-4</v>
       </c>
-    </row>
-    <row r="143" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN142" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO142" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP142" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ142" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR142" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS142" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT142" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU142" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV142" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW142" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX142" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>262</v>
       </c>
@@ -18766,8 +19250,41 @@
         <f t="shared" si="19"/>
         <v>4.0431038289007962E-4</v>
       </c>
-    </row>
-    <row r="144" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN143" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO143" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP143" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ143" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR143" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS143" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT143" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU143" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV143" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW143" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX143" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>263</v>
       </c>
@@ -18821,7 +19338,7 @@
         <v>6.785411243790979E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>264</v>
       </c>
@@ -18875,7 +19392,7 @@
         <v>7.2348983877483703E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>265</v>
       </c>
@@ -18928,8 +19445,11 @@
         <f t="shared" si="19"/>
         <v>6.5532909863160892E-4</v>
       </c>
-    </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN146" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>266</v>
       </c>
@@ -18982,8 +19502,35 @@
         <f t="shared" si="19"/>
         <v>7.5474341979737567E-4</v>
       </c>
-    </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN147" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO147" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BP147" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ147" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BR147" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BS147" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BT147" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU147" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BV147" s="4"/>
+      <c r="BW147" s="4"/>
+      <c r="BX147" s="4"/>
+    </row>
+    <row r="148" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>267</v>
       </c>
@@ -19036,8 +19583,32 @@
         <f t="shared" si="19"/>
         <v>5.7669688744116539E-4</v>
       </c>
-    </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN148" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU148" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>268</v>
       </c>
@@ -19090,8 +19661,32 @@
         <f t="shared" si="19"/>
         <v>8.0697176066542612E-4</v>
       </c>
-    </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN149" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO149" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP149" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ149" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR149" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS149" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT149" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU149" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>269</v>
       </c>
@@ -19144,8 +19739,32 @@
         <f t="shared" si="19"/>
         <v>6.0999509381094925E-4</v>
       </c>
-    </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN150" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO150" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP150" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ150" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR150" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS150" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT150" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU150" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>270</v>
       </c>
@@ -19198,8 +19817,32 @@
         <f t="shared" si="19"/>
         <v>5.3117803129513444E-4</v>
       </c>
-    </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN151" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU151" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>271</v>
       </c>
@@ -19252,8 +19895,32 @@
         <f t="shared" si="19"/>
         <v>6.8402085428227407E-4</v>
       </c>
-    </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN152" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO152" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP152" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ152" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR152" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS152" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT152" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU152" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>272</v>
       </c>
@@ -19306,8 +19973,32 @@
         <f t="shared" si="19"/>
         <v>5.6115552392589597E-4</v>
       </c>
-    </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN153" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO153" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP153" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ153" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR153" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS153" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT153" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU153" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>273</v>
       </c>
@@ -19360,8 +20051,32 @@
         <f t="shared" si="19"/>
         <v>5.6175108458420442E-4</v>
       </c>
-    </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN154" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU154" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>274</v>
       </c>
@@ -19389,8 +20104,32 @@
       <c r="I155">
         <v>36000</v>
       </c>
-    </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN155" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO155" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP155" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ155" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR155" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS155" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT155" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU155" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>275</v>
       </c>
@@ -19418,8 +20157,32 @@
       <c r="I156">
         <v>36000</v>
       </c>
-    </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN156" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO156" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP156" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ156" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR156" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS156" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT156" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU156" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>276</v>
       </c>
@@ -19447,8 +20210,32 @@
       <c r="I157">
         <v>36000</v>
       </c>
-    </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN157" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU157" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>277</v>
       </c>
@@ -19476,8 +20263,32 @@
       <c r="I158">
         <v>36000</v>
       </c>
-    </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN158" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO158" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP158" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ158" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR158" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS158" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT158" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU158" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>278</v>
       </c>
@@ -19505,8 +20316,32 @@
       <c r="I159">
         <v>36000</v>
       </c>
-    </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN159" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO159" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP159" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ159" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR159" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS159" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT159" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU159" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>279</v>
       </c>
@@ -19534,8 +20369,32 @@
       <c r="I160">
         <v>36000</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN160" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU160" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>280</v>
       </c>
@@ -19563,8 +20422,32 @@
       <c r="I161">
         <v>36000</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN161" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO161" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP161" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ161" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR161" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS161" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT161" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU161" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>281</v>
       </c>
@@ -19592,8 +20475,32 @@
       <c r="I162">
         <v>36000</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN162" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO162" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP162" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ162" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR162" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS162" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT162" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU162" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>282</v>
       </c>
@@ -19622,7 +20529,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>283</v>
       </c>
@@ -19651,7 +20558,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>284</v>
       </c>
@@ -19680,7 +20587,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>285</v>
       </c>
@@ -19709,7 +20616,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>286</v>
       </c>
@@ -19738,7 +20645,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>287</v>
       </c>
@@ -19767,7 +20674,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>288</v>
       </c>
@@ -19796,7 +20703,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>289</v>
       </c>
@@ -19825,7 +20732,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>290</v>
       </c>
@@ -19854,7 +20761,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>291</v>
       </c>
@@ -19883,7 +20790,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>292</v>
       </c>
@@ -19912,7 +20819,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>293</v>
       </c>
@@ -19941,7 +20848,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>294</v>
       </c>
@@ -19970,7 +20877,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>295</v>
       </c>
@@ -27392,8 +28299,8 @@
       <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22">
-        <v>5.5555555555555599E-4</v>
+      <c r="B22" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C22">
         <v>3.1154231364886891E-4</v>
@@ -27418,8 +28325,8 @@
       <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23">
-        <v>5.5555555555555599E-4</v>
+      <c r="B23" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C23">
         <v>3.1154231364886891E-5</v>
@@ -27444,8 +28351,8 @@
       <c r="A24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24">
-        <v>5.5555555555555599E-4</v>
+      <c r="B24" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C24">
         <v>3.1154231364886891E-4</v>
@@ -27470,8 +28377,8 @@
       <c r="A25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25">
-        <v>5.5555555555555599E-4</v>
+      <c r="B25" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C25">
         <v>3.1154231364886891E-5</v>
@@ -27496,8 +28403,8 @@
       <c r="A26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26">
-        <v>5.5555555555555599E-4</v>
+      <c r="B26" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C26">
         <v>3.1154231364886891E-4</v>
@@ -27683,19 +28590,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
@@ -27708,19 +28615,19 @@
         <v>3600000</v>
       </c>
       <c r="B3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
@@ -27733,19 +28640,19 @@
         <v>800000000</v>
       </c>
       <c r="B4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -44156,13 +45063,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>91</v>
       </c>
@@ -44182,7 +45089,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -44201,8 +45108,9 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -44221,8 +45129,9 @@
       <c r="F3" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -44241,8 +45150,9 @@
       <c r="F4" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -44261,8 +45171,9 @@
       <c r="F5" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -44281,8 +45192,9 @@
       <c r="F6" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -44301,8 +45213,9 @@
       <c r="F7" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -44321,8 +45234,9 @@
       <c r="F8" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -44341,8 +45255,9 @@
       <c r="F9" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -44361,8 +45276,9 @@
       <c r="F10" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -44381,8 +45297,9 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -44401,8 +45318,9 @@
       <c r="F12" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -44421,8 +45339,9 @@
       <c r="F13" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -44441,8 +45360,9 @@
       <c r="F14" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>97</v>
       </c>
@@ -44461,8 +45381,9 @@
       <c r="F15" s="4">
         <v>-50</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -44481,6 +45402,19 @@
       <c r="F16" s="4">
         <v>-50</v>
       </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
